--- a/data/hsi_vol_oos.xlsx
+++ b/data/hsi_vol_oos.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B946"/>
+  <dimension ref="A1:B951"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
         <v>44564</v>
       </c>
       <c r="B2" t="n">
-        <v>-2.677371049135569</v>
+        <v>-2.686753349883888</v>
       </c>
     </row>
     <row r="3">
@@ -459,7 +459,7 @@
         <v>44565</v>
       </c>
       <c r="B3" t="n">
-        <v>-2.677390347700695</v>
+        <v>-2.686997153726872</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         <v>44566</v>
       </c>
       <c r="B4" t="n">
-        <v>-2.699221036612564</v>
+        <v>-2.712447634092285</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         <v>44567</v>
       </c>
       <c r="B5" t="n">
-        <v>-2.665381422430695</v>
+        <v>-2.677758467495699</v>
       </c>
     </row>
     <row r="6">
@@ -483,7 +483,7 @@
         <v>44568</v>
       </c>
       <c r="B6" t="n">
-        <v>-2.697992390161802</v>
+        <v>-2.711836147692714</v>
       </c>
     </row>
     <row r="7">
@@ -491,7 +491,7 @@
         <v>44571</v>
       </c>
       <c r="B7" t="n">
-        <v>-2.707103801487149</v>
+        <v>-2.719873371115409</v>
       </c>
     </row>
     <row r="8">
@@ -499,7 +499,7 @@
         <v>44572</v>
       </c>
       <c r="B8" t="n">
-        <v>-2.687660441625027</v>
+        <v>-2.698838549470972</v>
       </c>
     </row>
     <row r="9">
@@ -507,7 +507,7 @@
         <v>44573</v>
       </c>
       <c r="B9" t="n">
-        <v>-2.759675494884642</v>
+        <v>-2.772542005561095</v>
       </c>
     </row>
     <row r="10">
@@ -515,7 +515,7 @@
         <v>44574</v>
       </c>
       <c r="B10" t="n">
-        <v>-2.734421738998116</v>
+        <v>-2.746667198549163</v>
       </c>
     </row>
     <row r="11">
@@ -523,7 +523,7 @@
         <v>44575</v>
       </c>
       <c r="B11" t="n">
-        <v>-2.73357760168419</v>
+        <v>-2.745996433868435</v>
       </c>
     </row>
     <row r="12">
@@ -531,7 +531,7 @@
         <v>44578</v>
       </c>
       <c r="B12" t="n">
-        <v>-2.703651237303451</v>
+        <v>-2.712612099361318</v>
       </c>
     </row>
     <row r="13">
@@ -539,7 +539,7 @@
         <v>44579</v>
       </c>
       <c r="B13" t="n">
-        <v>-2.701516168275581</v>
+        <v>-2.710114306917884</v>
       </c>
     </row>
     <row r="14">
@@ -547,7 +547,7 @@
         <v>44580</v>
       </c>
       <c r="B14" t="n">
-        <v>-2.614992336030064</v>
+        <v>-2.617666686329247</v>
       </c>
     </row>
     <row r="15">
@@ -555,7 +555,7 @@
         <v>44581</v>
       </c>
       <c r="B15" t="n">
-        <v>-2.745417396841394</v>
+        <v>-2.740491431776049</v>
       </c>
     </row>
     <row r="16">
@@ -563,7 +563,7 @@
         <v>44582</v>
       </c>
       <c r="B16" t="n">
-        <v>-2.637076284818884</v>
+        <v>-2.633188763444523</v>
       </c>
     </row>
     <row r="17">
@@ -571,7 +571,7 @@
         <v>44585</v>
       </c>
       <c r="B17" t="n">
-        <v>-2.644111400594215</v>
+        <v>-2.640180747236833</v>
       </c>
     </row>
     <row r="18">
@@ -579,7 +579,7 @@
         <v>44586</v>
       </c>
       <c r="B18" t="n">
-        <v>-2.673514909550296</v>
+        <v>-2.666533423270903</v>
       </c>
     </row>
     <row r="19">
@@ -587,7 +587,7 @@
         <v>44587</v>
       </c>
       <c r="B19" t="n">
-        <v>-2.673585454604841</v>
+        <v>-2.666533423270903</v>
       </c>
     </row>
     <row r="20">
@@ -595,7 +595,7 @@
         <v>44588</v>
       </c>
       <c r="B20" t="n">
-        <v>-2.689328712732741</v>
+        <v>-2.678505092872992</v>
       </c>
     </row>
     <row r="21">
@@ -603,7 +603,7 @@
         <v>44589</v>
       </c>
       <c r="B21" t="n">
-        <v>-2.695020580833446</v>
+        <v>-2.685253847181187</v>
       </c>
     </row>
     <row r="22">
@@ -611,7 +611,7 @@
         <v>44592</v>
       </c>
       <c r="B22" t="n">
-        <v>-2.646204139532127</v>
+        <v>-2.632751227034931</v>
       </c>
     </row>
     <row r="23">
@@ -619,7 +619,7 @@
         <v>44596</v>
       </c>
       <c r="B23" t="n">
-        <v>-2.580711573753516</v>
+        <v>-2.575054272733663</v>
       </c>
     </row>
     <row r="24">
@@ -627,7 +627,7 @@
         <v>44599</v>
       </c>
       <c r="B24" t="n">
-        <v>-2.558441322557073</v>
+        <v>-2.553103756590246</v>
       </c>
     </row>
     <row r="25">
@@ -635,7 +635,7 @@
         <v>44600</v>
       </c>
       <c r="B25" t="n">
-        <v>-2.563221695500937</v>
+        <v>-2.556678060531805</v>
       </c>
     </row>
     <row r="26">
@@ -643,7 +643,7 @@
         <v>44601</v>
       </c>
       <c r="B26" t="n">
-        <v>-2.575462916861271</v>
+        <v>-2.568751197379799</v>
       </c>
     </row>
     <row r="27">
@@ -651,7 +651,7 @@
         <v>44602</v>
       </c>
       <c r="B27" t="n">
-        <v>-2.559391701020798</v>
+        <v>-2.552432154554619</v>
       </c>
     </row>
     <row r="28">
@@ -659,7 +659,7 @@
         <v>44603</v>
       </c>
       <c r="B28" t="n">
-        <v>-2.392161234618732</v>
+        <v>-2.384188209851241</v>
       </c>
     </row>
     <row r="29">
@@ -667,7 +667,7 @@
         <v>44606</v>
       </c>
       <c r="B29" t="n">
-        <v>-2.218642348185889</v>
+        <v>-2.216143331259001</v>
       </c>
     </row>
     <row r="30">
@@ -675,7 +675,7 @@
         <v>44607</v>
       </c>
       <c r="B30" t="n">
-        <v>-1.991999561979839</v>
+        <v>-1.994972114489064</v>
       </c>
     </row>
     <row r="31">
@@ -683,7 +683,7 @@
         <v>44608</v>
       </c>
       <c r="B31" t="n">
-        <v>-1.889042718316567</v>
+        <v>-1.885891547011913</v>
       </c>
     </row>
     <row r="32">
@@ -691,7 +691,7 @@
         <v>44609</v>
       </c>
       <c r="B32" t="n">
-        <v>-1.889329502131265</v>
+        <v>-1.886224453960782</v>
       </c>
     </row>
     <row r="33">
@@ -699,7 +699,7 @@
         <v>44610</v>
       </c>
       <c r="B33" t="n">
-        <v>-1.892786896458748</v>
+        <v>-1.88996759846532</v>
       </c>
     </row>
     <row r="34">
@@ -707,7 +707,7 @@
         <v>44613</v>
       </c>
       <c r="B34" t="n">
-        <v>-1.872358147333694</v>
+        <v>-1.869669796795072</v>
       </c>
     </row>
     <row r="35">
@@ -715,7 +715,7 @@
         <v>44614</v>
       </c>
       <c r="B35" t="n">
-        <v>-1.887714171557204</v>
+        <v>-1.886455980246252</v>
       </c>
     </row>
     <row r="36">
@@ -723,7 +723,7 @@
         <v>44615</v>
       </c>
       <c r="B36" t="n">
-        <v>-1.887278914173551</v>
+        <v>-1.886283509856429</v>
       </c>
     </row>
     <row r="37">
@@ -731,7 +731,7 @@
         <v>44616</v>
       </c>
       <c r="B37" t="n">
-        <v>-1.894804587549609</v>
+        <v>-1.893762041257734</v>
       </c>
     </row>
     <row r="38">
@@ -739,7 +739,7 @@
         <v>44617</v>
       </c>
       <c r="B38" t="n">
-        <v>-1.891960977691084</v>
+        <v>-1.890384694984154</v>
       </c>
     </row>
     <row r="39">
@@ -747,7 +747,7 @@
         <v>44620</v>
       </c>
       <c r="B39" t="n">
-        <v>-1.88941472165258</v>
+        <v>-1.887848736807205</v>
       </c>
     </row>
     <row r="40">
@@ -755,7 +755,7 @@
         <v>44621</v>
       </c>
       <c r="B40" t="n">
-        <v>-1.885455775149675</v>
+        <v>-1.884409064335733</v>
       </c>
     </row>
     <row r="41">
@@ -763,7 +763,7 @@
         <v>44622</v>
       </c>
       <c r="B41" t="n">
-        <v>-1.890725614956988</v>
+        <v>-1.889890574847666</v>
       </c>
     </row>
     <row r="42">
@@ -771,7 +771,7 @@
         <v>44623</v>
       </c>
       <c r="B42" t="n">
-        <v>-1.891454994503261</v>
+        <v>-1.890716350658543</v>
       </c>
     </row>
     <row r="43">
@@ -779,7 +779,7 @@
         <v>44624</v>
       </c>
       <c r="B43" t="n">
-        <v>-1.897130014631459</v>
+        <v>-1.897128363125814</v>
       </c>
     </row>
     <row r="44">
@@ -787,7 +787,7 @@
         <v>44627</v>
       </c>
       <c r="B44" t="n">
-        <v>-1.925255781862716</v>
+        <v>-1.922752373879509</v>
       </c>
     </row>
     <row r="45">
@@ -795,7 +795,7 @@
         <v>44628</v>
       </c>
       <c r="B45" t="n">
-        <v>-1.928874390599319</v>
+        <v>-1.926117702528327</v>
       </c>
     </row>
     <row r="46">
@@ -803,7 +803,7 @@
         <v>44629</v>
       </c>
       <c r="B46" t="n">
-        <v>-1.92929925239453</v>
+        <v>-1.926350801860926</v>
       </c>
     </row>
     <row r="47">
@@ -811,7 +811,7 @@
         <v>44630</v>
       </c>
       <c r="B47" t="n">
-        <v>-1.911973957446179</v>
+        <v>-1.909141007934775</v>
       </c>
     </row>
     <row r="48">
@@ -819,7 +819,7 @@
         <v>44631</v>
       </c>
       <c r="B48" t="n">
-        <v>-1.916288563386051</v>
+        <v>-1.913332573988895</v>
       </c>
     </row>
     <row r="49">
@@ -827,7 +827,7 @@
         <v>44634</v>
       </c>
       <c r="B49" t="n">
-        <v>-1.974316902641301</v>
+        <v>-1.972214980181303</v>
       </c>
     </row>
     <row r="50">
@@ -835,7 +835,7 @@
         <v>44635</v>
       </c>
       <c r="B50" t="n">
-        <v>-2.077547491429397</v>
+        <v>-2.073121822295489</v>
       </c>
     </row>
     <row r="51">
@@ -843,7 +843,7 @@
         <v>44636</v>
       </c>
       <c r="B51" t="n">
-        <v>-2.335446174081746</v>
+        <v>-2.319234540218253</v>
       </c>
     </row>
     <row r="52">
@@ -851,7 +851,7 @@
         <v>44637</v>
       </c>
       <c r="B52" t="n">
-        <v>-2.658324236453693</v>
+        <v>-2.652058464749034</v>
       </c>
     </row>
     <row r="53">
@@ -859,7 +859,7 @@
         <v>44638</v>
       </c>
       <c r="B53" t="n">
-        <v>-2.642950254857292</v>
+        <v>-2.639174103081988</v>
       </c>
     </row>
     <row r="54">
@@ -867,7 +867,7 @@
         <v>44641</v>
       </c>
       <c r="B54" t="n">
-        <v>-2.656994582609546</v>
+        <v>-2.653306956062647</v>
       </c>
     </row>
     <row r="55">
@@ -875,7 +875,7 @@
         <v>44642</v>
       </c>
       <c r="B55" t="n">
-        <v>-2.647884255795401</v>
+        <v>-2.641156220877338</v>
       </c>
     </row>
     <row r="56">
@@ -883,7 +883,7 @@
         <v>44643</v>
       </c>
       <c r="B56" t="n">
-        <v>-2.661655628978432</v>
+        <v>-2.652693377100777</v>
       </c>
     </row>
     <row r="57">
@@ -891,7 +891,7 @@
         <v>44644</v>
       </c>
       <c r="B57" t="n">
-        <v>-2.668417521100713</v>
+        <v>-2.659340360232488</v>
       </c>
     </row>
     <row r="58">
@@ -899,7 +899,7 @@
         <v>44645</v>
       </c>
       <c r="B58" t="n">
-        <v>-2.725057364092724</v>
+        <v>-2.714986694075797</v>
       </c>
     </row>
     <row r="59">
@@ -907,7 +907,7 @@
         <v>44648</v>
       </c>
       <c r="B59" t="n">
-        <v>-2.578174220533442</v>
+        <v>-2.572886822768524</v>
       </c>
     </row>
     <row r="60">
@@ -915,7 +915,7 @@
         <v>44649</v>
       </c>
       <c r="B60" t="n">
-        <v>-2.588617864260845</v>
+        <v>-2.583209976979473</v>
       </c>
     </row>
     <row r="61">
@@ -923,7 +923,7 @@
         <v>44650</v>
       </c>
       <c r="B61" t="n">
-        <v>-2.595120640188251</v>
+        <v>-2.585744527248078</v>
       </c>
     </row>
     <row r="62">
@@ -931,7 +931,7 @@
         <v>44651</v>
       </c>
       <c r="B62" t="n">
-        <v>-2.596600831596446</v>
+        <v>-2.586275606489191</v>
       </c>
     </row>
     <row r="63">
@@ -939,7 +939,7 @@
         <v>44652</v>
       </c>
       <c r="B63" t="n">
-        <v>-2.486121642477031</v>
+        <v>-2.482975034963324</v>
       </c>
     </row>
     <row r="64">
@@ -947,7 +947,7 @@
         <v>44655</v>
       </c>
       <c r="B64" t="n">
-        <v>-2.4792761915814</v>
+        <v>-2.478618205184813</v>
       </c>
     </row>
     <row r="65">
@@ -955,7 +955,7 @@
         <v>44657</v>
       </c>
       <c r="B65" t="n">
-        <v>-2.493005480729269</v>
+        <v>-2.495743938765957</v>
       </c>
     </row>
     <row r="66">
@@ -963,7 +963,7 @@
         <v>44658</v>
       </c>
       <c r="B66" t="n">
-        <v>-2.455257851275021</v>
+        <v>-2.460226215270096</v>
       </c>
     </row>
     <row r="67">
@@ -971,7 +971,7 @@
         <v>44659</v>
       </c>
       <c r="B67" t="n">
-        <v>-2.405461110159564</v>
+        <v>-2.413906884191324</v>
       </c>
     </row>
     <row r="68">
@@ -979,7 +979,7 @@
         <v>44662</v>
       </c>
       <c r="B68" t="n">
-        <v>-2.469153797228912</v>
+        <v>-2.478339793602698</v>
       </c>
     </row>
     <row r="69">
@@ -987,7 +987,7 @@
         <v>44663</v>
       </c>
       <c r="B69" t="n">
-        <v>-2.401928134395052</v>
+        <v>-2.410266964264821</v>
       </c>
     </row>
     <row r="70">
@@ -995,7 +995,7 @@
         <v>44664</v>
       </c>
       <c r="B70" t="n">
-        <v>-2.402345150491075</v>
+        <v>-2.410690157960613</v>
       </c>
     </row>
     <row r="71">
@@ -1003,7 +1003,7 @@
         <v>44665</v>
       </c>
       <c r="B71" t="n">
-        <v>-2.375287626191289</v>
+        <v>-2.382851124793544</v>
       </c>
     </row>
     <row r="72">
@@ -1011,7 +1011,7 @@
         <v>44670</v>
       </c>
       <c r="B72" t="n">
-        <v>-2.360866835783344</v>
+        <v>-2.368229005740754</v>
       </c>
     </row>
     <row r="73">
@@ -1019,7 +1019,7 @@
         <v>44671</v>
       </c>
       <c r="B73" t="n">
-        <v>-2.354183448631075</v>
+        <v>-2.361906445679927</v>
       </c>
     </row>
     <row r="74">
@@ -1027,7 +1027,7 @@
         <v>44672</v>
       </c>
       <c r="B74" t="n">
-        <v>-2.352312305188354</v>
+        <v>-2.357189621826441</v>
       </c>
     </row>
     <row r="75">
@@ -1035,7 +1035,7 @@
         <v>44673</v>
       </c>
       <c r="B75" t="n">
-        <v>-2.352416695904047</v>
+        <v>-2.35690995276214</v>
       </c>
     </row>
     <row r="76">
@@ -1043,7 +1043,7 @@
         <v>44676</v>
       </c>
       <c r="B76" t="n">
-        <v>-2.414345804808622</v>
+        <v>-2.421370141879913</v>
       </c>
     </row>
     <row r="77">
@@ -1051,7 +1051,7 @@
         <v>44677</v>
       </c>
       <c r="B77" t="n">
-        <v>-2.360741738266415</v>
+        <v>-2.367097397851438</v>
       </c>
     </row>
     <row r="78">
@@ -1059,7 +1059,7 @@
         <v>44678</v>
       </c>
       <c r="B78" t="n">
-        <v>-2.340970275644262</v>
+        <v>-2.347096586977936</v>
       </c>
     </row>
     <row r="79">
@@ -1067,7 +1067,7 @@
         <v>44679</v>
       </c>
       <c r="B79" t="n">
-        <v>-2.336579558819418</v>
+        <v>-2.344103912478656</v>
       </c>
     </row>
     <row r="80">
@@ -1075,7 +1075,7 @@
         <v>44680</v>
       </c>
       <c r="B80" t="n">
-        <v>-2.431242318936549</v>
+        <v>-2.440244653567616</v>
       </c>
     </row>
     <row r="81">
@@ -1083,7 +1083,7 @@
         <v>44684</v>
       </c>
       <c r="B81" t="n">
-        <v>-2.426704485462466</v>
+        <v>-2.435620464881366</v>
       </c>
     </row>
     <row r="82">
@@ -1091,7 +1091,7 @@
         <v>44685</v>
       </c>
       <c r="B82" t="n">
-        <v>-2.394731003401394</v>
+        <v>-2.401478062497891</v>
       </c>
     </row>
     <row r="83">
@@ -1099,7 +1099,7 @@
         <v>44686</v>
       </c>
       <c r="B83" t="n">
-        <v>-2.394841686887345</v>
+        <v>-2.401592747754115</v>
       </c>
     </row>
     <row r="84">
@@ -1107,7 +1107,7 @@
         <v>44687</v>
       </c>
       <c r="B84" t="n">
-        <v>-2.454617978683102</v>
+        <v>-2.457374545824343</v>
       </c>
     </row>
     <row r="85">
@@ -1115,7 +1115,7 @@
         <v>44691</v>
       </c>
       <c r="B85" t="n">
-        <v>-2.484231217535346</v>
+        <v>-2.487125531615275</v>
       </c>
     </row>
     <row r="86">
@@ -1123,7 +1123,7 @@
         <v>44692</v>
       </c>
       <c r="B86" t="n">
-        <v>-2.495726486600792</v>
+        <v>-2.497581048076865</v>
       </c>
     </row>
     <row r="87">
@@ -1131,7 +1131,7 @@
         <v>44693</v>
       </c>
       <c r="B87" t="n">
-        <v>-2.450460032844934</v>
+        <v>-2.450337166968802</v>
       </c>
     </row>
     <row r="88">
@@ -1139,7 +1139,7 @@
         <v>44694</v>
       </c>
       <c r="B88" t="n">
-        <v>-2.505597357959878</v>
+        <v>-2.501250386839539</v>
       </c>
     </row>
     <row r="89">
@@ -1147,7 +1147,7 @@
         <v>44697</v>
       </c>
       <c r="B89" t="n">
-        <v>-2.493309156380029</v>
+        <v>-2.489440794710402</v>
       </c>
     </row>
     <row r="90">
@@ -1155,7 +1155,7 @@
         <v>44698</v>
       </c>
       <c r="B90" t="n">
-        <v>-2.534923612328711</v>
+        <v>-2.530676874039419</v>
       </c>
     </row>
     <row r="91">
@@ -1163,7 +1163,7 @@
         <v>44699</v>
       </c>
       <c r="B91" t="n">
-        <v>-2.521417527158504</v>
+        <v>-2.515349772702076</v>
       </c>
     </row>
     <row r="92">
@@ -1171,7 +1171,7 @@
         <v>44700</v>
       </c>
       <c r="B92" t="n">
-        <v>-2.560860007418035</v>
+        <v>-2.554760731201606</v>
       </c>
     </row>
     <row r="93">
@@ -1179,7 +1179,7 @@
         <v>44701</v>
       </c>
       <c r="B93" t="n">
-        <v>-2.603644017401483</v>
+        <v>-2.599773339081326</v>
       </c>
     </row>
     <row r="94">
@@ -1187,7 +1187,7 @@
         <v>44704</v>
       </c>
       <c r="B94" t="n">
-        <v>-2.556826545582498</v>
+        <v>-2.557195054475006</v>
       </c>
     </row>
     <row r="95">
@@ -1195,7 +1195,7 @@
         <v>44705</v>
       </c>
       <c r="B95" t="n">
-        <v>-2.55824392887578</v>
+        <v>-2.560942070835245</v>
       </c>
     </row>
     <row r="96">
@@ -1203,7 +1203,7 @@
         <v>44706</v>
       </c>
       <c r="B96" t="n">
-        <v>-2.528571989236661</v>
+        <v>-2.531522636065194</v>
       </c>
     </row>
     <row r="97">
@@ -1211,7 +1211,7 @@
         <v>44707</v>
       </c>
       <c r="B97" t="n">
-        <v>-2.485611689386998</v>
+        <v>-2.488355745733708</v>
       </c>
     </row>
     <row r="98">
@@ -1219,7 +1219,7 @@
         <v>44708</v>
       </c>
       <c r="B98" t="n">
-        <v>-2.551491387178098</v>
+        <v>-2.555519225231889</v>
       </c>
     </row>
     <row r="99">
@@ -1227,7 +1227,7 @@
         <v>44711</v>
       </c>
       <c r="B99" t="n">
-        <v>-2.562462135113291</v>
+        <v>-2.566533794137381</v>
       </c>
     </row>
     <row r="100">
@@ -1235,7 +1235,7 @@
         <v>44712</v>
       </c>
       <c r="B100" t="n">
-        <v>-2.579751683553556</v>
+        <v>-2.581609829881067</v>
       </c>
     </row>
     <row r="101">
@@ -1243,7 +1243,7 @@
         <v>44713</v>
       </c>
       <c r="B101" t="n">
-        <v>-2.581624199345832</v>
+        <v>-2.583491076948757</v>
       </c>
     </row>
     <row r="102">
@@ -1251,7 +1251,7 @@
         <v>44714</v>
       </c>
       <c r="B102" t="n">
-        <v>-2.587749306633778</v>
+        <v>-2.589430896056391</v>
       </c>
     </row>
     <row r="103">
@@ -1259,7 +1259,7 @@
         <v>44718</v>
       </c>
       <c r="B103" t="n">
-        <v>-2.630607010772872</v>
+        <v>-2.634714789613904</v>
       </c>
     </row>
     <row r="104">
@@ -1267,7 +1267,7 @@
         <v>44719</v>
       </c>
       <c r="B104" t="n">
-        <v>-2.628763677889411</v>
+        <v>-2.631666751517801</v>
       </c>
     </row>
     <row r="105">
@@ -1275,7 +1275,7 @@
         <v>44720</v>
       </c>
       <c r="B105" t="n">
-        <v>-2.672181892836077</v>
+        <v>-2.675307728682063</v>
       </c>
     </row>
     <row r="106">
@@ -1283,7 +1283,7 @@
         <v>44721</v>
       </c>
       <c r="B106" t="n">
-        <v>-2.610044743303786</v>
+        <v>-2.608412532999583</v>
       </c>
     </row>
     <row r="107">
@@ -1291,7 +1291,7 @@
         <v>44722</v>
       </c>
       <c r="B107" t="n">
-        <v>-2.592428684842178</v>
+        <v>-2.593310166824907</v>
       </c>
     </row>
     <row r="108">
@@ -1299,7 +1299,7 @@
         <v>44725</v>
       </c>
       <c r="B108" t="n">
-        <v>-2.722937205855635</v>
+        <v>-2.724219727650629</v>
       </c>
     </row>
     <row r="109">
@@ -1307,7 +1307,7 @@
         <v>44726</v>
       </c>
       <c r="B109" t="n">
-        <v>-2.720384314203739</v>
+        <v>-2.721764151316506</v>
       </c>
     </row>
     <row r="110">
@@ -1315,7 +1315,7 @@
         <v>44727</v>
       </c>
       <c r="B110" t="n">
-        <v>-2.698717544194068</v>
+        <v>-2.700059376459198</v>
       </c>
     </row>
     <row r="111">
@@ -1323,7 +1323,7 @@
         <v>44728</v>
       </c>
       <c r="B111" t="n">
-        <v>-2.68732298724782</v>
+        <v>-2.688645976363572</v>
       </c>
     </row>
     <row r="112">
@@ -1331,7 +1331,7 @@
         <v>44729</v>
       </c>
       <c r="B112" t="n">
-        <v>-2.701520290531995</v>
+        <v>-2.705702104544375</v>
       </c>
     </row>
     <row r="113">
@@ -1339,7 +1339,7 @@
         <v>44732</v>
       </c>
       <c r="B113" t="n">
-        <v>-2.691342415271289</v>
+        <v>-2.694783069158845</v>
       </c>
     </row>
     <row r="114">
@@ -1347,7 +1347,7 @@
         <v>44733</v>
       </c>
       <c r="B114" t="n">
-        <v>-2.696911258602745</v>
+        <v>-2.693523568587281</v>
       </c>
     </row>
     <row r="115">
@@ -1355,7 +1355,7 @@
         <v>44734</v>
       </c>
       <c r="B115" t="n">
-        <v>-2.776867905772872</v>
+        <v>-2.766782344306241</v>
       </c>
     </row>
     <row r="116">
@@ -1363,7 +1363,7 @@
         <v>44735</v>
       </c>
       <c r="B116" t="n">
-        <v>-2.799201265600235</v>
+        <v>-2.78863901031898</v>
       </c>
     </row>
     <row r="117">
@@ -1371,7 +1371,7 @@
         <v>44736</v>
       </c>
       <c r="B117" t="n">
-        <v>-2.815004699589463</v>
+        <v>-2.804093360219622</v>
       </c>
     </row>
     <row r="118">
@@ -1379,7 +1379,7 @@
         <v>44739</v>
       </c>
       <c r="B118" t="n">
-        <v>-2.880044557288194</v>
+        <v>-2.867576303229758</v>
       </c>
     </row>
     <row r="119">
@@ -1387,7 +1387,7 @@
         <v>44740</v>
       </c>
       <c r="B119" t="n">
-        <v>-2.886731845403852</v>
+        <v>-2.871291066747379</v>
       </c>
     </row>
     <row r="120">
@@ -1395,7 +1395,7 @@
         <v>44741</v>
       </c>
       <c r="B120" t="n">
-        <v>-2.846972119352254</v>
+        <v>-2.83870934692312</v>
       </c>
     </row>
     <row r="121">
@@ -1403,7 +1403,7 @@
         <v>44742</v>
       </c>
       <c r="B121" t="n">
-        <v>-2.849957154296058</v>
+        <v>-2.841647951934617</v>
       </c>
     </row>
     <row r="122">
@@ -1411,7 +1411,7 @@
         <v>44746</v>
       </c>
       <c r="B122" t="n">
-        <v>-2.773605890434077</v>
+        <v>-2.766533330966727</v>
       </c>
     </row>
     <row r="123">
@@ -1419,7 +1419,7 @@
         <v>44747</v>
       </c>
       <c r="B123" t="n">
-        <v>-2.772174676426885</v>
+        <v>-2.764967009877112</v>
       </c>
     </row>
     <row r="124">
@@ -1427,7 +1427,7 @@
         <v>44748</v>
       </c>
       <c r="B124" t="n">
-        <v>-2.742158531791259</v>
+        <v>-2.740563973780957</v>
       </c>
     </row>
     <row r="125">
@@ -1435,7 +1435,7 @@
         <v>44749</v>
       </c>
       <c r="B125" t="n">
-        <v>-2.746561089837441</v>
+        <v>-2.746783237787371</v>
       </c>
     </row>
     <row r="126">
@@ -1443,7 +1443,7 @@
         <v>44750</v>
       </c>
       <c r="B126" t="n">
-        <v>-2.739694444464029</v>
+        <v>-2.741606472339263</v>
       </c>
     </row>
     <row r="127">
@@ -1451,7 +1451,7 @@
         <v>44753</v>
       </c>
       <c r="B127" t="n">
-        <v>-2.824382307125449</v>
+        <v>-2.832531478552126</v>
       </c>
     </row>
     <row r="128">
@@ -1459,7 +1459,7 @@
         <v>44754</v>
       </c>
       <c r="B128" t="n">
-        <v>-2.800337554600183</v>
+        <v>-2.812132950028914</v>
       </c>
     </row>
     <row r="129">
@@ -1467,7 +1467,7 @@
         <v>44755</v>
       </c>
       <c r="B129" t="n">
-        <v>-2.735741528298203</v>
+        <v>-2.751392463227528</v>
       </c>
     </row>
     <row r="130">
@@ -1475,7 +1475,7 @@
         <v>44756</v>
       </c>
       <c r="B130" t="n">
-        <v>-2.734353857006528</v>
+        <v>-2.748468574932728</v>
       </c>
     </row>
     <row r="131">
@@ -1483,7 +1483,7 @@
         <v>44757</v>
       </c>
       <c r="B131" t="n">
-        <v>-2.773275622117809</v>
+        <v>-2.788511049796613</v>
       </c>
     </row>
     <row r="132">
@@ -1491,7 +1491,7 @@
         <v>44760</v>
       </c>
       <c r="B132" t="n">
-        <v>-2.837505502407021</v>
+        <v>-2.85479935731635</v>
       </c>
     </row>
     <row r="133">
@@ -1499,7 +1499,7 @@
         <v>44761</v>
       </c>
       <c r="B133" t="n">
-        <v>-2.841582379006648</v>
+        <v>-2.859016435308458</v>
       </c>
     </row>
     <row r="134">
@@ -1507,7 +1507,7 @@
         <v>44762</v>
       </c>
       <c r="B134" t="n">
-        <v>-2.852232000990384</v>
+        <v>-2.868083295445154</v>
       </c>
     </row>
     <row r="135">
@@ -1515,7 +1515,7 @@
         <v>44763</v>
       </c>
       <c r="B135" t="n">
-        <v>-2.892019884677709</v>
+        <v>-2.913950434848644</v>
       </c>
     </row>
     <row r="136">
@@ -1523,7 +1523,7 @@
         <v>44764</v>
       </c>
       <c r="B136" t="n">
-        <v>-2.891033358825726</v>
+        <v>-2.913444052339819</v>
       </c>
     </row>
     <row r="137">
@@ -1531,7 +1531,7 @@
         <v>44767</v>
       </c>
       <c r="B137" t="n">
-        <v>-2.870462512945817</v>
+        <v>-2.890105572356913</v>
       </c>
     </row>
     <row r="138">
@@ -1539,7 +1539,7 @@
         <v>44768</v>
       </c>
       <c r="B138" t="n">
-        <v>-2.889809790519458</v>
+        <v>-2.908222126370712</v>
       </c>
     </row>
     <row r="139">
@@ -1547,7 +1547,7 @@
         <v>44769</v>
       </c>
       <c r="B139" t="n">
-        <v>-2.738439374721948</v>
+        <v>-2.756168436446696</v>
       </c>
     </row>
     <row r="140">
@@ -1555,7 +1555,7 @@
         <v>44770</v>
       </c>
       <c r="B140" t="n">
-        <v>-2.731306034740213</v>
+        <v>-2.746360158336818</v>
       </c>
     </row>
     <row r="141">
@@ -1563,7 +1563,7 @@
         <v>44771</v>
       </c>
       <c r="B141" t="n">
-        <v>-2.785832383683029</v>
+        <v>-2.793044852562944</v>
       </c>
     </row>
     <row r="142">
@@ -1571,7 +1571,7 @@
         <v>44774</v>
       </c>
       <c r="B142" t="n">
-        <v>-2.785052245005343</v>
+        <v>-2.792918072309105</v>
       </c>
     </row>
     <row r="143">
@@ -1579,7 +1579,7 @@
         <v>44775</v>
       </c>
       <c r="B143" t="n">
-        <v>-2.863280778941563</v>
+        <v>-2.872443936536759</v>
       </c>
     </row>
     <row r="144">
@@ -1587,7 +1587,7 @@
         <v>44776</v>
       </c>
       <c r="B144" t="n">
-        <v>-2.834738501746275</v>
+        <v>-2.84187151665389</v>
       </c>
     </row>
     <row r="145">
@@ -1595,7 +1595,7 @@
         <v>44777</v>
       </c>
       <c r="B145" t="n">
-        <v>-2.886313094269714</v>
+        <v>-2.8909989206153</v>
       </c>
     </row>
     <row r="146">
@@ -1603,7 +1603,7 @@
         <v>44778</v>
       </c>
       <c r="B146" t="n">
-        <v>-2.865902455599247</v>
+        <v>-2.868135449267931</v>
       </c>
     </row>
     <row r="147">
@@ -1611,7 +1611,7 @@
         <v>44781</v>
       </c>
       <c r="B147" t="n">
-        <v>-2.875268764968181</v>
+        <v>-2.87528290140616</v>
       </c>
     </row>
     <row r="148">
@@ -1619,7 +1619,7 @@
         <v>44782</v>
       </c>
       <c r="B148" t="n">
-        <v>-2.867746980748824</v>
+        <v>-2.868761852053917</v>
       </c>
     </row>
     <row r="149">
@@ -1627,7 +1627,7 @@
         <v>44783</v>
       </c>
       <c r="B149" t="n">
-        <v>-2.913708243052712</v>
+        <v>-2.904061799631669</v>
       </c>
     </row>
     <row r="150">
@@ -1635,7 +1635,7 @@
         <v>44784</v>
       </c>
       <c r="B150" t="n">
-        <v>-2.883492010285346</v>
+        <v>-2.867637653496607</v>
       </c>
     </row>
     <row r="151">
@@ -1643,7 +1643,7 @@
         <v>44785</v>
       </c>
       <c r="B151" t="n">
-        <v>-2.888270247131133</v>
+        <v>-2.874450243447153</v>
       </c>
     </row>
     <row r="152">
@@ -1651,7 +1651,7 @@
         <v>44788</v>
       </c>
       <c r="B152" t="n">
-        <v>-2.813822356555513</v>
+        <v>-2.798691674002051</v>
       </c>
     </row>
     <row r="153">
@@ -1659,7 +1659,7 @@
         <v>44789</v>
       </c>
       <c r="B153" t="n">
-        <v>-2.8323972785024</v>
+        <v>-2.816281449780142</v>
       </c>
     </row>
     <row r="154">
@@ -1667,7 +1667,7 @@
         <v>44790</v>
       </c>
       <c r="B154" t="n">
-        <v>-2.827198095287407</v>
+        <v>-2.809062428332513</v>
       </c>
     </row>
     <row r="155">
@@ -1675,7 +1675,7 @@
         <v>44791</v>
       </c>
       <c r="B155" t="n">
-        <v>-2.812105652896354</v>
+        <v>-2.799363919430469</v>
       </c>
     </row>
     <row r="156">
@@ -1683,7 +1683,7 @@
         <v>44792</v>
       </c>
       <c r="B156" t="n">
-        <v>-2.789525736788515</v>
+        <v>-2.777738706147084</v>
       </c>
     </row>
     <row r="157">
@@ -1691,7 +1691,7 @@
         <v>44795</v>
       </c>
       <c r="B157" t="n">
-        <v>-2.755032302874285</v>
+        <v>-2.741664914118052</v>
       </c>
     </row>
     <row r="158">
@@ -1699,7 +1699,7 @@
         <v>44796</v>
       </c>
       <c r="B158" t="n">
-        <v>-2.738366579964425</v>
+        <v>-2.728760440530921</v>
       </c>
     </row>
     <row r="159">
@@ -1707,7 +1707,7 @@
         <v>44797</v>
       </c>
       <c r="B159" t="n">
-        <v>-2.739228250252317</v>
+        <v>-2.728034072747687</v>
       </c>
     </row>
     <row r="160">
@@ -1715,7 +1715,7 @@
         <v>44798</v>
       </c>
       <c r="B160" t="n">
-        <v>-2.911599877472502</v>
+        <v>-2.891111016724561</v>
       </c>
     </row>
     <row r="161">
@@ -1723,7 +1723,7 @@
         <v>44799</v>
       </c>
       <c r="B161" t="n">
-        <v>-2.9230494655142</v>
+        <v>-2.90644730925499</v>
       </c>
     </row>
     <row r="162">
@@ -1731,7 +1731,7 @@
         <v>44802</v>
       </c>
       <c r="B162" t="n">
-        <v>-2.76017443001893</v>
+        <v>-2.751819500382187</v>
       </c>
     </row>
     <row r="163">
@@ -1739,7 +1739,7 @@
         <v>44803</v>
       </c>
       <c r="B163" t="n">
-        <v>-2.7570073768638</v>
+        <v>-2.748096298795844</v>
       </c>
     </row>
     <row r="164">
@@ -1747,7 +1747,7 @@
         <v>44804</v>
       </c>
       <c r="B164" t="n">
-        <v>-2.754548017179778</v>
+        <v>-2.745005669324009</v>
       </c>
     </row>
     <row r="165">
@@ -1755,7 +1755,7 @@
         <v>44805</v>
       </c>
       <c r="B165" t="n">
-        <v>-2.768586117132239</v>
+        <v>-2.759142476031468</v>
       </c>
     </row>
     <row r="166">
@@ -1763,7 +1763,7 @@
         <v>44806</v>
       </c>
       <c r="B166" t="n">
-        <v>-2.480207742817206</v>
+        <v>-2.474876709031018</v>
       </c>
     </row>
     <row r="167">
@@ -1771,7 +1771,7 @@
         <v>44809</v>
       </c>
       <c r="B167" t="n">
-        <v>-2.488794906913647</v>
+        <v>-2.484218168993201</v>
       </c>
     </row>
     <row r="168">
@@ -1779,7 +1779,7 @@
         <v>44810</v>
       </c>
       <c r="B168" t="n">
-        <v>-2.473613005540895</v>
+        <v>-2.468064684136171</v>
       </c>
     </row>
     <row r="169">
@@ -1787,7 +1787,7 @@
         <v>44811</v>
       </c>
       <c r="B169" t="n">
-        <v>-2.419945564971769</v>
+        <v>-2.414896800234483</v>
       </c>
     </row>
     <row r="170">
@@ -1795,7 +1795,7 @@
         <v>44812</v>
       </c>
       <c r="B170" t="n">
-        <v>-2.396604106890727</v>
+        <v>-2.395204051527009</v>
       </c>
     </row>
     <row r="171">
@@ -1803,7 +1803,7 @@
         <v>44813</v>
       </c>
       <c r="B171" t="n">
-        <v>-2.436100744896373</v>
+        <v>-2.434590615565003</v>
       </c>
     </row>
     <row r="172">
@@ -1811,7 +1811,7 @@
         <v>44817</v>
       </c>
       <c r="B172" t="n">
-        <v>-2.418113914612524</v>
+        <v>-2.416567625627807</v>
       </c>
     </row>
     <row r="173">
@@ -1819,7 +1819,7 @@
         <v>44818</v>
       </c>
       <c r="B173" t="n">
-        <v>-2.445352453078068</v>
+        <v>-2.44691945913362</v>
       </c>
     </row>
     <row r="174">
@@ -1827,7 +1827,7 @@
         <v>44819</v>
       </c>
       <c r="B174" t="n">
-        <v>-2.445766478428779</v>
+        <v>-2.447527211186582</v>
       </c>
     </row>
     <row r="175">
@@ -1835,7 +1835,7 @@
         <v>44820</v>
       </c>
       <c r="B175" t="n">
-        <v>-2.427015824503164</v>
+        <v>-2.429755197068838</v>
       </c>
     </row>
     <row r="176">
@@ -1843,7 +1843,7 @@
         <v>44823</v>
       </c>
       <c r="B176" t="n">
-        <v>-2.407401590663544</v>
+        <v>-2.405465899750439</v>
       </c>
     </row>
     <row r="177">
@@ -1851,7 +1851,7 @@
         <v>44824</v>
       </c>
       <c r="B177" t="n">
-        <v>-2.404501421277287</v>
+        <v>-2.40255089971016</v>
       </c>
     </row>
     <row r="178">
@@ -1859,7 +1859,7 @@
         <v>44825</v>
       </c>
       <c r="B178" t="n">
-        <v>-2.420901082816743</v>
+        <v>-2.420225055288278</v>
       </c>
     </row>
     <row r="179">
@@ -1867,7 +1867,7 @@
         <v>44826</v>
       </c>
       <c r="B179" t="n">
-        <v>-2.218279520842031</v>
+        <v>-2.220560570214198</v>
       </c>
     </row>
     <row r="180">
@@ -1875,7 +1875,7 @@
         <v>44827</v>
       </c>
       <c r="B180" t="n">
-        <v>-2.223638290678602</v>
+        <v>-2.22702521448978</v>
       </c>
     </row>
     <row r="181">
@@ -1883,7 +1883,7 @@
         <v>44830</v>
       </c>
       <c r="B181" t="n">
-        <v>-2.220844466146431</v>
+        <v>-2.224006422569648</v>
       </c>
     </row>
     <row r="182">
@@ -1891,7 +1891,7 @@
         <v>44831</v>
       </c>
       <c r="B182" t="n">
-        <v>-2.218894727431173</v>
+        <v>-2.188824262488873</v>
       </c>
     </row>
     <row r="183">
@@ -1899,7 +1899,7 @@
         <v>44832</v>
       </c>
       <c r="B183" t="n">
-        <v>-2.071295813206467</v>
+        <v>-2.179257730057827</v>
       </c>
     </row>
     <row r="184">
@@ -1907,7 +1907,7 @@
         <v>44833</v>
       </c>
       <c r="B184" t="n">
-        <v>-2.069500176861343</v>
+        <v>-2.177944660044579</v>
       </c>
     </row>
     <row r="185">
@@ -1915,7 +1915,7 @@
         <v>44834</v>
       </c>
       <c r="B185" t="n">
-        <v>-2.002242050324409</v>
+        <v>-2.095949015328229</v>
       </c>
     </row>
     <row r="186">
@@ -1923,7 +1923,7 @@
         <v>44837</v>
       </c>
       <c r="B186" t="n">
-        <v>-1.989719845379492</v>
+        <v>-2.082197070741005</v>
       </c>
     </row>
     <row r="187">
@@ -1931,7 +1931,7 @@
         <v>44839</v>
       </c>
       <c r="B187" t="n">
-        <v>-2.051015998988559</v>
+        <v>-2.156920567057125</v>
       </c>
     </row>
     <row r="188">
@@ -1939,7 +1939,7 @@
         <v>44840</v>
       </c>
       <c r="B188" t="n">
-        <v>-1.977829535229608</v>
+        <v>-2.06792525934609</v>
       </c>
     </row>
     <row r="189">
@@ -1947,7 +1947,7 @@
         <v>44841</v>
       </c>
       <c r="B189" t="n">
-        <v>-1.964036072194136</v>
+        <v>-2.051941682358939</v>
       </c>
     </row>
     <row r="190">
@@ -1955,7 +1955,7 @@
         <v>44844</v>
       </c>
       <c r="B190" t="n">
-        <v>-1.986247593153662</v>
+        <v>-2.078556648428548</v>
       </c>
     </row>
     <row r="191">
@@ -1963,7 +1963,7 @@
         <v>44845</v>
       </c>
       <c r="B191" t="n">
-        <v>-1.993462905624222</v>
+        <v>-2.086749484130825</v>
       </c>
     </row>
     <row r="192">
@@ -1971,7 +1971,7 @@
         <v>44846</v>
       </c>
       <c r="B192" t="n">
-        <v>-1.988392015339518</v>
+        <v>-2.080652403555512</v>
       </c>
     </row>
     <row r="193">
@@ -1979,7 +1979,7 @@
         <v>44847</v>
       </c>
       <c r="B193" t="n">
-        <v>-1.870306629610775</v>
+        <v>-1.9418401130674</v>
       </c>
     </row>
     <row r="194">
@@ -1987,7 +1987,7 @@
         <v>44848</v>
       </c>
       <c r="B194" t="n">
-        <v>-1.866758212509333</v>
+        <v>-1.938064675390771</v>
       </c>
     </row>
     <row r="195">
@@ -1995,7 +1995,7 @@
         <v>44851</v>
       </c>
       <c r="B195" t="n">
-        <v>-1.833757574094762</v>
+        <v>-1.89816990438687</v>
       </c>
     </row>
     <row r="196">
@@ -2003,7 +2003,7 @@
         <v>44852</v>
       </c>
       <c r="B196" t="n">
-        <v>-1.840144444441932</v>
+        <v>-1.905219130782648</v>
       </c>
     </row>
     <row r="197">
@@ -2011,7 +2011,7 @@
         <v>44853</v>
       </c>
       <c r="B197" t="n">
-        <v>-1.846815479480952</v>
+        <v>-1.913694703085427</v>
       </c>
     </row>
     <row r="198">
@@ -2019,7 +2019,7 @@
         <v>44854</v>
       </c>
       <c r="B198" t="n">
-        <v>-1.850535272871463</v>
+        <v>-1.918314780211549</v>
       </c>
     </row>
     <row r="199">
@@ -2027,7 +2027,7 @@
         <v>44855</v>
       </c>
       <c r="B199" t="n">
-        <v>-1.845516399043543</v>
+        <v>-1.91162811283076</v>
       </c>
     </row>
     <row r="200">
@@ -2035,7 +2035,7 @@
         <v>44858</v>
       </c>
       <c r="B200" t="n">
-        <v>-1.932761352808845</v>
+        <v>-2.010705059625556</v>
       </c>
     </row>
     <row r="201">
@@ -2043,7 +2043,7 @@
         <v>44859</v>
       </c>
       <c r="B201" t="n">
-        <v>-1.931650667941944</v>
+        <v>-2.009802422938348</v>
       </c>
     </row>
     <row r="202">
@@ -2051,7 +2051,7 @@
         <v>44860</v>
       </c>
       <c r="B202" t="n">
-        <v>-1.932490847129319</v>
+        <v>-2.010006874555267</v>
       </c>
     </row>
     <row r="203">
@@ -2059,7 +2059,7 @@
         <v>44861</v>
       </c>
       <c r="B203" t="n">
-        <v>-1.933001419127347</v>
+        <v>-2.033452847401403</v>
       </c>
     </row>
     <row r="204">
@@ -2067,7 +2067,7 @@
         <v>44862</v>
       </c>
       <c r="B204" t="n">
-        <v>-2.068844006597399</v>
+        <v>-2.069216045056663</v>
       </c>
     </row>
     <row r="205">
@@ -2075,7 +2075,7 @@
         <v>44865</v>
       </c>
       <c r="B205" t="n">
-        <v>-1.997386999100434</v>
+        <v>-1.997148849861962</v>
       </c>
     </row>
     <row r="206">
@@ -2083,7 +2083,7 @@
         <v>44866</v>
       </c>
       <c r="B206" t="n">
-        <v>-2.050963041447051</v>
+        <v>-2.051292526832164</v>
       </c>
     </row>
     <row r="207">
@@ -2091,7 +2091,7 @@
         <v>44867</v>
       </c>
       <c r="B207" t="n">
-        <v>-2.064101325234271</v>
+        <v>-2.063138631792475</v>
       </c>
     </row>
     <row r="208">
@@ -2099,7 +2099,7 @@
         <v>44868</v>
       </c>
       <c r="B208" t="n">
-        <v>-2.094094323136245</v>
+        <v>-2.092321981920696</v>
       </c>
     </row>
     <row r="209">
@@ -2107,7 +2107,7 @@
         <v>44869</v>
       </c>
       <c r="B209" t="n">
-        <v>-2.124057835286946</v>
+        <v>-2.122049721345849</v>
       </c>
     </row>
     <row r="210">
@@ -2115,7 +2115,7 @@
         <v>44872</v>
       </c>
       <c r="B210" t="n">
-        <v>-2.150897972990442</v>
+        <v>-2.148808112936145</v>
       </c>
     </row>
     <row r="211">
@@ -2123,7 +2123,7 @@
         <v>44873</v>
       </c>
       <c r="B211" t="n">
-        <v>-2.117448340815882</v>
+        <v>-2.114422312029201</v>
       </c>
     </row>
     <row r="212">
@@ -2131,7 +2131,7 @@
         <v>44874</v>
       </c>
       <c r="B212" t="n">
-        <v>-2.094413779239846</v>
+        <v>-2.089475727182852</v>
       </c>
     </row>
     <row r="213">
@@ -2139,7 +2139,7 @@
         <v>44875</v>
       </c>
       <c r="B213" t="n">
-        <v>-2.085037032650116</v>
+        <v>-2.081657141151475</v>
       </c>
     </row>
     <row r="214">
@@ -2147,7 +2147,7 @@
         <v>44876</v>
       </c>
       <c r="B214" t="n">
-        <v>-2.27236983892089</v>
+        <v>-2.26714732594007</v>
       </c>
     </row>
     <row r="215">
@@ -2155,7 +2155,7 @@
         <v>44879</v>
       </c>
       <c r="B215" t="n">
-        <v>-2.283492591024057</v>
+        <v>-2.276362196326297</v>
       </c>
     </row>
     <row r="216">
@@ -2163,7 +2163,7 @@
         <v>44880</v>
       </c>
       <c r="B216" t="n">
-        <v>-2.368387759122726</v>
+        <v>-2.364869800615206</v>
       </c>
     </row>
     <row r="217">
@@ -2171,7 +2171,7 @@
         <v>44881</v>
       </c>
       <c r="B217" t="n">
-        <v>-2.356071570507753</v>
+        <v>-2.354013507668831</v>
       </c>
     </row>
     <row r="218">
@@ -2179,7 +2179,7 @@
         <v>44882</v>
       </c>
       <c r="B218" t="n">
-        <v>-2.361003420019816</v>
+        <v>-2.359626891874702</v>
       </c>
     </row>
     <row r="219">
@@ -2187,7 +2187,7 @@
         <v>44883</v>
       </c>
       <c r="B219" t="n">
-        <v>-2.360936792976681</v>
+        <v>-2.358693081806018</v>
       </c>
     </row>
     <row r="220">
@@ -2195,7 +2195,7 @@
         <v>44886</v>
       </c>
       <c r="B220" t="n">
-        <v>-2.363034296582283</v>
+        <v>-2.362002971731788</v>
       </c>
     </row>
     <row r="221">
@@ -2203,7 +2203,7 @@
         <v>44887</v>
       </c>
       <c r="B221" t="n">
-        <v>-2.374666765623579</v>
+        <v>-2.372442650500618</v>
       </c>
     </row>
     <row r="222">
@@ -2211,7 +2211,7 @@
         <v>44888</v>
       </c>
       <c r="B222" t="n">
-        <v>-2.337841622375467</v>
+        <v>-2.337876242329474</v>
       </c>
     </row>
     <row r="223">
@@ -2219,7 +2219,7 @@
         <v>44889</v>
       </c>
       <c r="B223" t="n">
-        <v>-2.339361052437364</v>
+        <v>-2.341156711473351</v>
       </c>
     </row>
     <row r="224">
@@ -2227,7 +2227,7 @@
         <v>44890</v>
       </c>
       <c r="B224" t="n">
-        <v>-2.326074672275559</v>
+        <v>-2.327255372829788</v>
       </c>
     </row>
     <row r="225">
@@ -2235,7 +2235,7 @@
         <v>44893</v>
       </c>
       <c r="B225" t="n">
-        <v>-2.333784403917503</v>
+        <v>-2.334063931193107</v>
       </c>
     </row>
     <row r="226">
@@ -2243,7 +2243,7 @@
         <v>44894</v>
       </c>
       <c r="B226" t="n">
-        <v>-2.489921241559206</v>
+        <v>-2.490685453278337</v>
       </c>
     </row>
     <row r="227">
@@ -2251,7 +2251,7 @@
         <v>44895</v>
       </c>
       <c r="B227" t="n">
-        <v>-2.501550434951048</v>
+        <v>-2.500620693959935</v>
       </c>
     </row>
     <row r="228">
@@ -2259,7 +2259,7 @@
         <v>44896</v>
       </c>
       <c r="B228" t="n">
-        <v>-2.442528853275891</v>
+        <v>-2.438459882968984</v>
       </c>
     </row>
     <row r="229">
@@ -2267,7 +2267,7 @@
         <v>44897</v>
       </c>
       <c r="B229" t="n">
-        <v>-2.435162600697781</v>
+        <v>-2.432640714081428</v>
       </c>
     </row>
     <row r="230">
@@ -2275,7 +2275,7 @@
         <v>44900</v>
       </c>
       <c r="B230" t="n">
-        <v>-2.562980879358285</v>
+        <v>-2.56003109994198</v>
       </c>
     </row>
     <row r="231">
@@ -2283,7 +2283,7 @@
         <v>44901</v>
       </c>
       <c r="B231" t="n">
-        <v>-2.534253133154339</v>
+        <v>-2.534127905079762</v>
       </c>
     </row>
     <row r="232">
@@ -2291,7 +2291,7 @@
         <v>44902</v>
       </c>
       <c r="B232" t="n">
-        <v>-2.614160622706213</v>
+        <v>-2.617368670745945</v>
       </c>
     </row>
     <row r="233">
@@ -2299,7 +2299,7 @@
         <v>44903</v>
       </c>
       <c r="B233" t="n">
-        <v>-2.700380376161889</v>
+        <v>-2.70705992721132</v>
       </c>
     </row>
     <row r="234">
@@ -2307,7 +2307,7 @@
         <v>44904</v>
       </c>
       <c r="B234" t="n">
-        <v>-2.762888623041997</v>
+        <v>-2.764986344723259</v>
       </c>
     </row>
     <row r="235">
@@ -2315,7 +2315,7 @@
         <v>44907</v>
       </c>
       <c r="B235" t="n">
-        <v>-2.808546672342443</v>
+        <v>-2.810921303857032</v>
       </c>
     </row>
     <row r="236">
@@ -2323,7 +2323,7 @@
         <v>44908</v>
       </c>
       <c r="B236" t="n">
-        <v>-2.81649699262847</v>
+        <v>-2.818918199903423</v>
       </c>
     </row>
     <row r="237">
@@ -2331,7 +2331,7 @@
         <v>44909</v>
       </c>
       <c r="B237" t="n">
-        <v>-2.812019461935558</v>
+        <v>-2.814888313246308</v>
       </c>
     </row>
     <row r="238">
@@ -2339,7 +2339,7 @@
         <v>44910</v>
       </c>
       <c r="B238" t="n">
-        <v>-2.840906482853984</v>
+        <v>-2.841683323389428</v>
       </c>
     </row>
     <row r="239">
@@ -2347,7 +2347,7 @@
         <v>44911</v>
       </c>
       <c r="B239" t="n">
-        <v>-2.845446776027972</v>
+        <v>-2.845851563581837</v>
       </c>
     </row>
     <row r="240">
@@ -2355,7 +2355,7 @@
         <v>44914</v>
       </c>
       <c r="B240" t="n">
-        <v>-2.807359005722665</v>
+        <v>-2.803314668994048</v>
       </c>
     </row>
     <row r="241">
@@ -2363,7 +2363,7 @@
         <v>44915</v>
       </c>
       <c r="B241" t="n">
-        <v>-2.763554911723426</v>
+        <v>-2.759242271714884</v>
       </c>
     </row>
     <row r="242">
@@ -2371,7 +2371,7 @@
         <v>44916</v>
       </c>
       <c r="B242" t="n">
-        <v>-2.764026548814301</v>
+        <v>-2.760529520273812</v>
       </c>
     </row>
     <row r="243">
@@ -2379,7 +2379,7 @@
         <v>44917</v>
       </c>
       <c r="B243" t="n">
-        <v>-2.780947871458308</v>
+        <v>-2.764962830330922</v>
       </c>
     </row>
     <row r="244">
@@ -2387,7 +2387,7 @@
         <v>44918</v>
       </c>
       <c r="B244" t="n">
-        <v>-2.769090034331222</v>
+        <v>-2.755196630487253</v>
       </c>
     </row>
     <row r="245">
@@ -2395,7 +2395,7 @@
         <v>44923</v>
       </c>
       <c r="B245" t="n">
-        <v>-2.794377960448098</v>
+        <v>-2.784000290915</v>
       </c>
     </row>
     <row r="246">
@@ -2403,7 +2403,7 @@
         <v>44924</v>
       </c>
       <c r="B246" t="n">
-        <v>-2.804415221261442</v>
+        <v>-2.793296315193153</v>
       </c>
     </row>
     <row r="247">
@@ -2411,7 +2411,7 @@
         <v>44925</v>
       </c>
       <c r="B247" t="n">
-        <v>-2.777093727819416</v>
+        <v>-2.770509300587917</v>
       </c>
     </row>
     <row r="248">
@@ -2419,7 +2419,7 @@
         <v>44929</v>
       </c>
       <c r="B248" t="n">
-        <v>-2.762853050605455</v>
+        <v>-2.7588263397188</v>
       </c>
     </row>
     <row r="249">
@@ -2427,7 +2427,7 @@
         <v>44930</v>
       </c>
       <c r="B249" t="n">
-        <v>-2.898861611945155</v>
+        <v>-2.905327056155109</v>
       </c>
     </row>
     <row r="250">
@@ -2435,7 +2435,7 @@
         <v>44931</v>
       </c>
       <c r="B250" t="n">
-        <v>-2.92452820359723</v>
+        <v>-2.9314643360764</v>
       </c>
     </row>
     <row r="251">
@@ -2443,7 +2443,7 @@
         <v>44932</v>
       </c>
       <c r="B251" t="n">
-        <v>-2.879762231644403</v>
+        <v>-2.890947409641028</v>
       </c>
     </row>
     <row r="252">
@@ -2451,7 +2451,7 @@
         <v>44935</v>
       </c>
       <c r="B252" t="n">
-        <v>-2.863573558452561</v>
+        <v>-2.868970847667778</v>
       </c>
     </row>
     <row r="253">
@@ -2459,7 +2459,7 @@
         <v>44936</v>
       </c>
       <c r="B253" t="n">
-        <v>-2.864637612867571</v>
+        <v>-2.868962738725971</v>
       </c>
     </row>
     <row r="254">
@@ -2467,7 +2467,7 @@
         <v>44937</v>
       </c>
       <c r="B254" t="n">
-        <v>-2.866494367747581</v>
+        <v>-2.870366560918515</v>
       </c>
     </row>
     <row r="255">
@@ -2475,7 +2475,7 @@
         <v>44938</v>
       </c>
       <c r="B255" t="n">
-        <v>-2.8336610621206</v>
+        <v>-2.840953679190951</v>
       </c>
     </row>
     <row r="256">
@@ -2483,7 +2483,7 @@
         <v>44939</v>
       </c>
       <c r="B256" t="n">
-        <v>-2.835394154579669</v>
+        <v>-2.842711072786806</v>
       </c>
     </row>
     <row r="257">
@@ -2491,7 +2491,7 @@
         <v>44942</v>
       </c>
       <c r="B257" t="n">
-        <v>-2.813743930312679</v>
+        <v>-2.820769056352856</v>
       </c>
     </row>
     <row r="258">
@@ -2499,7 +2499,7 @@
         <v>44943</v>
       </c>
       <c r="B258" t="n">
-        <v>-2.813284742466188</v>
+        <v>-2.821970772598745</v>
       </c>
     </row>
     <row r="259">
@@ -2507,7 +2507,7 @@
         <v>44944</v>
       </c>
       <c r="B259" t="n">
-        <v>-2.781577733258504</v>
+        <v>-2.793764572875846</v>
       </c>
     </row>
     <row r="260">
@@ -2515,7 +2515,7 @@
         <v>44945</v>
       </c>
       <c r="B260" t="n">
-        <v>-2.77728786844419</v>
+        <v>-2.788084754637142</v>
       </c>
     </row>
     <row r="261">
@@ -2523,7 +2523,7 @@
         <v>44946</v>
       </c>
       <c r="B261" t="n">
-        <v>-2.815356312293697</v>
+        <v>-2.832607429777968</v>
       </c>
     </row>
     <row r="262">
@@ -2531,7 +2531,7 @@
         <v>44952</v>
       </c>
       <c r="B262" t="n">
-        <v>-2.877489124652885</v>
+        <v>-2.900465917445281</v>
       </c>
     </row>
     <row r="263">
@@ -2539,7 +2539,7 @@
         <v>44953</v>
       </c>
       <c r="B263" t="n">
-        <v>-2.869102047313153</v>
+        <v>-2.891288179916409</v>
       </c>
     </row>
     <row r="264">
@@ -2547,7 +2547,7 @@
         <v>44956</v>
       </c>
       <c r="B264" t="n">
-        <v>-2.963399863617744</v>
+        <v>-2.999460814215108</v>
       </c>
     </row>
     <row r="265">
@@ -2555,7 +2555,7 @@
         <v>44957</v>
       </c>
       <c r="B265" t="n">
-        <v>-2.751765030307338</v>
+        <v>-2.784938605456835</v>
       </c>
     </row>
     <row r="266">
@@ -2563,7 +2563,7 @@
         <v>44958</v>
       </c>
       <c r="B266" t="n">
-        <v>-2.75449454811922</v>
+        <v>-2.785797083837267</v>
       </c>
     </row>
     <row r="267">
@@ -2571,7 +2571,7 @@
         <v>44959</v>
       </c>
       <c r="B267" t="n">
-        <v>-2.749179225446799</v>
+        <v>-2.778585505109021</v>
       </c>
     </row>
     <row r="268">
@@ -2579,7 +2579,7 @@
         <v>44960</v>
       </c>
       <c r="B268" t="n">
-        <v>-2.777500070874534</v>
+        <v>-2.803310618334575</v>
       </c>
     </row>
     <row r="269">
@@ -2587,7 +2587,7 @@
         <v>44963</v>
       </c>
       <c r="B269" t="n">
-        <v>-2.829651576933855</v>
+        <v>-2.855532360361711</v>
       </c>
     </row>
     <row r="270">
@@ -2595,7 +2595,7 @@
         <v>44964</v>
       </c>
       <c r="B270" t="n">
-        <v>-2.75859301523932</v>
+        <v>-2.779757209638826</v>
       </c>
     </row>
     <row r="271">
@@ -2603,7 +2603,7 @@
         <v>44965</v>
       </c>
       <c r="B271" t="n">
-        <v>-2.756750756404223</v>
+        <v>-2.777724703790108</v>
       </c>
     </row>
     <row r="272">
@@ -2611,7 +2611,7 @@
         <v>44966</v>
       </c>
       <c r="B272" t="n">
-        <v>-2.664803685057745</v>
+        <v>-2.673681602450953</v>
       </c>
     </row>
     <row r="273">
@@ -2619,7 +2619,7 @@
         <v>44967</v>
       </c>
       <c r="B273" t="n">
-        <v>-2.664985266906064</v>
+        <v>-2.671615687871315</v>
       </c>
     </row>
     <row r="274">
@@ -2627,7 +2627,7 @@
         <v>44970</v>
       </c>
       <c r="B274" t="n">
-        <v>-2.609407341227177</v>
+        <v>-2.617885752144352</v>
       </c>
     </row>
     <row r="275">
@@ -2635,7 +2635,7 @@
         <v>44971</v>
       </c>
       <c r="B275" t="n">
-        <v>-2.585153629379095</v>
+        <v>-2.595478373503352</v>
       </c>
     </row>
     <row r="276">
@@ -2643,7 +2643,7 @@
         <v>44972</v>
       </c>
       <c r="B276" t="n">
-        <v>-2.577412834834678</v>
+        <v>-2.585132742832087</v>
       </c>
     </row>
     <row r="277">
@@ -2651,7 +2651,7 @@
         <v>44973</v>
       </c>
       <c r="B277" t="n">
-        <v>-2.563720665158775</v>
+        <v>-2.571234059149162</v>
       </c>
     </row>
     <row r="278">
@@ -2659,7 +2659,7 @@
         <v>44974</v>
       </c>
       <c r="B278" t="n">
-        <v>-2.518634738399789</v>
+        <v>-2.52332677928127</v>
       </c>
     </row>
     <row r="279">
@@ -2667,7 +2667,7 @@
         <v>44977</v>
       </c>
       <c r="B279" t="n">
-        <v>-2.51075859777031</v>
+        <v>-2.512988843031894</v>
       </c>
     </row>
     <row r="280">
@@ -2675,7 +2675,7 @@
         <v>44978</v>
       </c>
       <c r="B280" t="n">
-        <v>-2.507512374872762</v>
+        <v>-2.508121320452947</v>
       </c>
     </row>
     <row r="281">
@@ -2683,7 +2683,7 @@
         <v>44979</v>
       </c>
       <c r="B281" t="n">
-        <v>-2.472422973959238</v>
+        <v>-2.473076650073134</v>
       </c>
     </row>
     <row r="282">
@@ -2691,7 +2691,7 @@
         <v>44980</v>
       </c>
       <c r="B282" t="n">
-        <v>-2.470581907661631</v>
+        <v>-2.46927254904986</v>
       </c>
     </row>
     <row r="283">
@@ -2699,7 +2699,7 @@
         <v>44981</v>
       </c>
       <c r="B283" t="n">
-        <v>-2.459507100465959</v>
+        <v>-2.459933609877337</v>
       </c>
     </row>
     <row r="284">
@@ -2707,7 +2707,7 @@
         <v>44984</v>
       </c>
       <c r="B284" t="n">
-        <v>-2.457237762852216</v>
+        <v>-2.455107843769182</v>
       </c>
     </row>
     <row r="285">
@@ -2715,7 +2715,7 @@
         <v>44985</v>
       </c>
       <c r="B285" t="n">
-        <v>-2.430014859432615</v>
+        <v>-2.432944371479941</v>
       </c>
     </row>
     <row r="286">
@@ -2723,7 +2723,7 @@
         <v>44986</v>
       </c>
       <c r="B286" t="n">
-        <v>-2.537106737835014</v>
+        <v>-2.531755903178881</v>
       </c>
     </row>
     <row r="287">
@@ -2731,7 +2731,7 @@
         <v>44987</v>
       </c>
       <c r="B287" t="n">
-        <v>-2.540972584995265</v>
+        <v>-2.535831749487976</v>
       </c>
     </row>
     <row r="288">
@@ -2739,7 +2739,7 @@
         <v>44988</v>
       </c>
       <c r="B288" t="n">
-        <v>-2.545505847695832</v>
+        <v>-2.541826179642552</v>
       </c>
     </row>
     <row r="289">
@@ -2747,7 +2747,7 @@
         <v>44991</v>
       </c>
       <c r="B289" t="n">
-        <v>-2.541818810095023</v>
+        <v>-2.539154173578346</v>
       </c>
     </row>
     <row r="290">
@@ -2755,7 +2755,7 @@
         <v>44992</v>
       </c>
       <c r="B290" t="n">
-        <v>-2.542327188650707</v>
+        <v>-2.539659369468955</v>
       </c>
     </row>
     <row r="291">
@@ -2763,7 +2763,7 @@
         <v>44993</v>
       </c>
       <c r="B291" t="n">
-        <v>-2.582844569708534</v>
+        <v>-2.579198546310448</v>
       </c>
     </row>
     <row r="292">
@@ -2771,7 +2771,7 @@
         <v>44994</v>
       </c>
       <c r="B292" t="n">
-        <v>-2.576809381330296</v>
+        <v>-2.572428833731399</v>
       </c>
     </row>
     <row r="293">
@@ -2779,7 +2779,7 @@
         <v>44995</v>
       </c>
       <c r="B293" t="n">
-        <v>-2.681140407110095</v>
+        <v>-2.681083656793636</v>
       </c>
     </row>
     <row r="294">
@@ -2787,7 +2787,7 @@
         <v>44998</v>
       </c>
       <c r="B294" t="n">
-        <v>-2.726672573782531</v>
+        <v>-2.729178485881986</v>
       </c>
     </row>
     <row r="295">
@@ -2795,7 +2795,7 @@
         <v>44999</v>
       </c>
       <c r="B295" t="n">
-        <v>-2.767385913412379</v>
+        <v>-2.767013743127424</v>
       </c>
     </row>
     <row r="296">
@@ -2803,7 +2803,7 @@
         <v>45000</v>
       </c>
       <c r="B296" t="n">
-        <v>-2.796700233672713</v>
+        <v>-2.791935976719489</v>
       </c>
     </row>
     <row r="297">
@@ -2811,7 +2811,7 @@
         <v>45001</v>
       </c>
       <c r="B297" t="n">
-        <v>-2.811539036017597</v>
+        <v>-2.810332932733371</v>
       </c>
     </row>
     <row r="298">
@@ -2819,7 +2819,7 @@
         <v>45002</v>
       </c>
       <c r="B298" t="n">
-        <v>-2.846925262411508</v>
+        <v>-2.845612407436194</v>
       </c>
     </row>
     <row r="299">
@@ -2827,7 +2827,7 @@
         <v>45005</v>
       </c>
       <c r="B299" t="n">
-        <v>-2.91048772529127</v>
+        <v>-2.91372690488609</v>
       </c>
     </row>
     <row r="300">
@@ -2835,7 +2835,7 @@
         <v>45006</v>
       </c>
       <c r="B300" t="n">
-        <v>-2.934487212343395</v>
+        <v>-2.940128929487739</v>
       </c>
     </row>
     <row r="301">
@@ -2843,7 +2843,7 @@
         <v>45007</v>
       </c>
       <c r="B301" t="n">
-        <v>-2.933395277340166</v>
+        <v>-2.942049005537098</v>
       </c>
     </row>
     <row r="302">
@@ -2851,7 +2851,7 @@
         <v>45008</v>
       </c>
       <c r="B302" t="n">
-        <v>-3.027489663058823</v>
+        <v>-3.040361133355163</v>
       </c>
     </row>
     <row r="303">
@@ -2859,7 +2859,7 @@
         <v>45009</v>
       </c>
       <c r="B303" t="n">
-        <v>-3.030451045025187</v>
+        <v>-3.047534163639627</v>
       </c>
     </row>
     <row r="304">
@@ -2867,7 +2867,7 @@
         <v>45012</v>
       </c>
       <c r="B304" t="n">
-        <v>-3.09833279505971</v>
+        <v>-3.111343487914133</v>
       </c>
     </row>
     <row r="305">
@@ -2875,7 +2875,7 @@
         <v>45013</v>
       </c>
       <c r="B305" t="n">
-        <v>-3.121974981869864</v>
+        <v>-3.146184725601912</v>
       </c>
     </row>
     <row r="306">
@@ -2883,7 +2883,7 @@
         <v>45014</v>
       </c>
       <c r="B306" t="n">
-        <v>-3.20217323982838</v>
+        <v>-3.216493098320969</v>
       </c>
     </row>
     <row r="307">
@@ -2891,7 +2891,7 @@
         <v>45015</v>
       </c>
       <c r="B307" t="n">
-        <v>-3.15931017818509</v>
+        <v>-3.171687068025152</v>
       </c>
     </row>
     <row r="308">
@@ -2899,7 +2899,7 @@
         <v>45016</v>
       </c>
       <c r="B308" t="n">
-        <v>-3.155680541465793</v>
+        <v>-3.167100846097182</v>
       </c>
     </row>
     <row r="309">
@@ -2907,7 +2907,7 @@
         <v>45019</v>
       </c>
       <c r="B309" t="n">
-        <v>-3.113300758656541</v>
+        <v>-3.129365476809881</v>
       </c>
     </row>
     <row r="310">
@@ -2915,7 +2915,7 @@
         <v>45020</v>
       </c>
       <c r="B310" t="n">
-        <v>-3.008291410890682</v>
+        <v>-3.025610991402088</v>
       </c>
     </row>
     <row r="311">
@@ -2923,7 +2923,7 @@
         <v>45022</v>
       </c>
       <c r="B311" t="n">
-        <v>-3.00586350027375</v>
+        <v>-3.0230981241912</v>
       </c>
     </row>
     <row r="312">
@@ -2931,7 +2931,7 @@
         <v>45027</v>
       </c>
       <c r="B312" t="n">
-        <v>-3.019925727645732</v>
+        <v>-3.03938957562469</v>
       </c>
     </row>
     <row r="313">
@@ -2939,7 +2939,7 @@
         <v>45028</v>
       </c>
       <c r="B313" t="n">
-        <v>-3.029505828326367</v>
+        <v>-3.053383303473401</v>
       </c>
     </row>
     <row r="314">
@@ -2947,7 +2947,7 @@
         <v>45029</v>
       </c>
       <c r="B314" t="n">
-        <v>-2.966513226441489</v>
+        <v>-2.982225325578714</v>
       </c>
     </row>
     <row r="315">
@@ -2955,7 +2955,7 @@
         <v>45030</v>
       </c>
       <c r="B315" t="n">
-        <v>-2.975238510082867</v>
+        <v>-2.991271852744345</v>
       </c>
     </row>
     <row r="316">
@@ -2963,7 +2963,7 @@
         <v>45033</v>
       </c>
       <c r="B316" t="n">
-        <v>-2.934570805296702</v>
+        <v>-2.947391284761748</v>
       </c>
     </row>
     <row r="317">
@@ -2971,7 +2971,7 @@
         <v>45034</v>
       </c>
       <c r="B317" t="n">
-        <v>-2.931062082880411</v>
+        <v>-2.944086603034281</v>
       </c>
     </row>
     <row r="318">
@@ -2979,7 +2979,7 @@
         <v>45035</v>
       </c>
       <c r="B318" t="n">
-        <v>-2.938683996926041</v>
+        <v>-2.940809136727759</v>
       </c>
     </row>
     <row r="319">
@@ -2987,7 +2987,7 @@
         <v>45036</v>
       </c>
       <c r="B319" t="n">
-        <v>-2.915625321975085</v>
+        <v>-2.915590284342316</v>
       </c>
     </row>
     <row r="320">
@@ -2995,7 +2995,7 @@
         <v>45037</v>
       </c>
       <c r="B320" t="n">
-        <v>-2.947454487320154</v>
+        <v>-2.944109819145318</v>
       </c>
     </row>
     <row r="321">
@@ -3003,7 +3003,7 @@
         <v>45040</v>
       </c>
       <c r="B321" t="n">
-        <v>-2.90618644790582</v>
+        <v>-2.90818025904278</v>
       </c>
     </row>
     <row r="322">
@@ -3011,7 +3011,7 @@
         <v>45041</v>
       </c>
       <c r="B322" t="n">
-        <v>-2.906116185094521</v>
+        <v>-2.903789939512725</v>
       </c>
     </row>
     <row r="323">
@@ -3019,7 +3019,7 @@
         <v>45042</v>
       </c>
       <c r="B323" t="n">
-        <v>-2.894427888015103</v>
+        <v>-2.892161494537519</v>
       </c>
     </row>
     <row r="324">
@@ -3027,7 +3027,7 @@
         <v>45043</v>
       </c>
       <c r="B324" t="n">
-        <v>-2.898214117334896</v>
+        <v>-2.896368634120789</v>
       </c>
     </row>
     <row r="325">
@@ -3035,7 +3035,7 @@
         <v>45044</v>
       </c>
       <c r="B325" t="n">
-        <v>-2.840733230347695</v>
+        <v>-2.84523529684875</v>
       </c>
     </row>
     <row r="326">
@@ -3043,7 +3043,7 @@
         <v>45048</v>
       </c>
       <c r="B326" t="n">
-        <v>-2.840674697862182</v>
+        <v>-2.844186937577899</v>
       </c>
     </row>
     <row r="327">
@@ -3051,7 +3051,7 @@
         <v>45049</v>
       </c>
       <c r="B327" t="n">
-        <v>-2.65952812237257</v>
+        <v>-2.658597934603558</v>
       </c>
     </row>
     <row r="328">
@@ -3059,7 +3059,7 @@
         <v>45050</v>
       </c>
       <c r="B328" t="n">
-        <v>-2.670682818734262</v>
+        <v>-2.671882253347105</v>
       </c>
     </row>
     <row r="329">
@@ -3067,7 +3067,7 @@
         <v>45051</v>
       </c>
       <c r="B329" t="n">
-        <v>-2.673020889627342</v>
+        <v>-2.674026431533957</v>
       </c>
     </row>
     <row r="330">
@@ -3075,7 +3075,7 @@
         <v>45054</v>
       </c>
       <c r="B330" t="n">
-        <v>-2.682292521662726</v>
+        <v>-2.679730567705845</v>
       </c>
     </row>
     <row r="331">
@@ -3083,7 +3083,7 @@
         <v>45055</v>
       </c>
       <c r="B331" t="n">
-        <v>-2.738246917900994</v>
+        <v>-2.731897259051251</v>
       </c>
     </row>
     <row r="332">
@@ -3091,7 +3091,7 @@
         <v>45056</v>
       </c>
       <c r="B332" t="n">
-        <v>-2.736582790304794</v>
+        <v>-2.730594151939853</v>
       </c>
     </row>
     <row r="333">
@@ -3099,7 +3099,7 @@
         <v>45057</v>
       </c>
       <c r="B333" t="n">
-        <v>-2.736214034414327</v>
+        <v>-2.730137995675047</v>
       </c>
     </row>
     <row r="334">
@@ -3107,7 +3107,7 @@
         <v>45058</v>
       </c>
       <c r="B334" t="n">
-        <v>-2.736566970997972</v>
+        <v>-2.728680681755772</v>
       </c>
     </row>
     <row r="335">
@@ -3115,7 +3115,7 @@
         <v>45061</v>
       </c>
       <c r="B335" t="n">
-        <v>-2.771551109824561</v>
+        <v>-2.765307617984942</v>
       </c>
     </row>
     <row r="336">
@@ -3123,7 +3123,7 @@
         <v>45062</v>
       </c>
       <c r="B336" t="n">
-        <v>-2.717790762626079</v>
+        <v>-2.707258781672088</v>
       </c>
     </row>
     <row r="337">
@@ -3131,7 +3131,7 @@
         <v>45063</v>
       </c>
       <c r="B337" t="n">
-        <v>-2.75816358044788</v>
+        <v>-2.750532689199705</v>
       </c>
     </row>
     <row r="338">
@@ -3139,7 +3139,7 @@
         <v>45064</v>
       </c>
       <c r="B338" t="n">
-        <v>-2.761993428330117</v>
+        <v>-2.75601526713157</v>
       </c>
     </row>
     <row r="339">
@@ -3147,7 +3147,7 @@
         <v>45065</v>
       </c>
       <c r="B339" t="n">
-        <v>-2.758542010456531</v>
+        <v>-2.756804452033526</v>
       </c>
     </row>
     <row r="340">
@@ -3155,7 +3155,7 @@
         <v>45068</v>
       </c>
       <c r="B340" t="n">
-        <v>-2.73132185291949</v>
+        <v>-2.732193830840536</v>
       </c>
     </row>
     <row r="341">
@@ -3163,7 +3163,7 @@
         <v>45069</v>
       </c>
       <c r="B341" t="n">
-        <v>-2.710828428639013</v>
+        <v>-2.7157388007027</v>
       </c>
     </row>
     <row r="342">
@@ -3171,7 +3171,7 @@
         <v>45070</v>
       </c>
       <c r="B342" t="n">
-        <v>-2.737599999102432</v>
+        <v>-2.740191374278149</v>
       </c>
     </row>
     <row r="343">
@@ -3179,7 +3179,7 @@
         <v>45071</v>
       </c>
       <c r="B343" t="n">
-        <v>-2.739354091500867</v>
+        <v>-2.743037170367735</v>
       </c>
     </row>
     <row r="344">
@@ -3187,7 +3187,7 @@
         <v>45075</v>
       </c>
       <c r="B344" t="n">
-        <v>-2.750840234780515</v>
+        <v>-2.754603009559223</v>
       </c>
     </row>
     <row r="345">
@@ -3195,7 +3195,7 @@
         <v>45076</v>
       </c>
       <c r="B345" t="n">
-        <v>-2.729819279895905</v>
+        <v>-2.733437257521907</v>
       </c>
     </row>
     <row r="346">
@@ -3203,7 +3203,7 @@
         <v>45077</v>
       </c>
       <c r="B346" t="n">
-        <v>-2.775719619918283</v>
+        <v>-2.774272016865658</v>
       </c>
     </row>
     <row r="347">
@@ -3211,7 +3211,7 @@
         <v>45078</v>
       </c>
       <c r="B347" t="n">
-        <v>-2.726796885806184</v>
+        <v>-2.7259587919546</v>
       </c>
     </row>
     <row r="348">
@@ -3219,7 +3219,7 @@
         <v>45079</v>
       </c>
       <c r="B348" t="n">
-        <v>-2.962305498554624</v>
+        <v>-2.958689318331507</v>
       </c>
     </row>
     <row r="349">
@@ -3227,7 +3227,7 @@
         <v>45082</v>
       </c>
       <c r="B349" t="n">
-        <v>-2.935053063551595</v>
+        <v>-2.931641370018544</v>
       </c>
     </row>
     <row r="350">
@@ -3235,7 +3235,7 @@
         <v>45083</v>
       </c>
       <c r="B350" t="n">
-        <v>-2.846829492126724</v>
+        <v>-2.844286753233897</v>
       </c>
     </row>
     <row r="351">
@@ -3243,7 +3243,7 @@
         <v>45084</v>
       </c>
       <c r="B351" t="n">
-        <v>-2.847629966898999</v>
+        <v>-2.846466768042121</v>
       </c>
     </row>
     <row r="352">
@@ -3251,7 +3251,7 @@
         <v>45085</v>
       </c>
       <c r="B352" t="n">
-        <v>-2.844056297470835</v>
+        <v>-2.841920403805946</v>
       </c>
     </row>
     <row r="353">
@@ -3259,7 +3259,7 @@
         <v>45086</v>
       </c>
       <c r="B353" t="n">
-        <v>-2.838744777825198</v>
+        <v>-2.836220316496588</v>
       </c>
     </row>
     <row r="354">
@@ -3267,7 +3267,7 @@
         <v>45089</v>
       </c>
       <c r="B354" t="n">
-        <v>-2.819601028425109</v>
+        <v>-2.818163160334702</v>
       </c>
     </row>
     <row r="355">
@@ -3275,7 +3275,7 @@
         <v>45090</v>
       </c>
       <c r="B355" t="n">
-        <v>-2.738451785572777</v>
+        <v>-2.74263322674841</v>
       </c>
     </row>
     <row r="356">
@@ -3283,7 +3283,7 @@
         <v>45091</v>
       </c>
       <c r="B356" t="n">
-        <v>-2.742140964184143</v>
+        <v>-2.747105576527596</v>
       </c>
     </row>
     <row r="357">
@@ -3291,7 +3291,7 @@
         <v>45092</v>
       </c>
       <c r="B357" t="n">
-        <v>-2.748521015874859</v>
+        <v>-2.810286786798162</v>
       </c>
     </row>
     <row r="358">
@@ -3299,7 +3299,7 @@
         <v>45093</v>
       </c>
       <c r="B358" t="n">
-        <v>-2.761954469233595</v>
+        <v>-2.771257413743401</v>
       </c>
     </row>
     <row r="359">
@@ -3307,7 +3307,7 @@
         <v>45096</v>
       </c>
       <c r="B359" t="n">
-        <v>-2.76742462806637</v>
+        <v>-2.775717801390789</v>
       </c>
     </row>
     <row r="360">
@@ -3315,7 +3315,7 @@
         <v>45097</v>
       </c>
       <c r="B360" t="n">
-        <v>-2.782084499298171</v>
+        <v>-2.800890009259529</v>
       </c>
     </row>
     <row r="361">
@@ -3323,7 +3323,7 @@
         <v>45098</v>
       </c>
       <c r="B361" t="n">
-        <v>-2.766573685028156</v>
+        <v>-2.836905373141667</v>
       </c>
     </row>
     <row r="362">
@@ -3331,7 +3331,7 @@
         <v>45100</v>
       </c>
       <c r="B362" t="n">
-        <v>-2.629630606135152</v>
+        <v>-2.808224817534503</v>
       </c>
     </row>
     <row r="363">
@@ -3339,7 +3339,7 @@
         <v>45103</v>
       </c>
       <c r="B363" t="n">
-        <v>-2.630367233882211</v>
+        <v>-2.635605116616833</v>
       </c>
     </row>
     <row r="364">
@@ -3347,7 +3347,7 @@
         <v>45104</v>
       </c>
       <c r="B364" t="n">
-        <v>-2.643250650435297</v>
+        <v>-2.663917161199616</v>
       </c>
     </row>
     <row r="365">
@@ -3355,7 +3355,7 @@
         <v>45105</v>
       </c>
       <c r="B365" t="n">
-        <v>-2.622701764786064</v>
+        <v>-2.647444155049651</v>
       </c>
     </row>
     <row r="366">
@@ -3363,7 +3363,7 @@
         <v>45106</v>
       </c>
       <c r="B366" t="n">
-        <v>-2.636687545375612</v>
+        <v>-2.643529696881981</v>
       </c>
     </row>
     <row r="367">
@@ -3371,7 +3371,7 @@
         <v>45107</v>
       </c>
       <c r="B367" t="n">
-        <v>-2.636595078383584</v>
+        <v>-2.640252274154579</v>
       </c>
     </row>
     <row r="368">
@@ -3379,7 +3379,7 @@
         <v>45110</v>
       </c>
       <c r="B368" t="n">
-        <v>-2.610990921812303</v>
+        <v>-2.681420573330509</v>
       </c>
     </row>
     <row r="369">
@@ -3387,7 +3387,7 @@
         <v>45111</v>
       </c>
       <c r="B369" t="n">
-        <v>-2.611050339228978</v>
+        <v>-2.611868905599593</v>
       </c>
     </row>
     <row r="370">
@@ -3395,7 +3395,7 @@
         <v>45112</v>
       </c>
       <c r="B370" t="n">
-        <v>-2.626675876060161</v>
+        <v>-2.630614393631838</v>
       </c>
     </row>
     <row r="371">
@@ -3403,7 +3403,7 @@
         <v>45113</v>
       </c>
       <c r="B371" t="n">
-        <v>-2.681815200643693</v>
+        <v>-2.681025747108414</v>
       </c>
     </row>
     <row r="372">
@@ -3411,7 +3411,7 @@
         <v>45114</v>
       </c>
       <c r="B372" t="n">
-        <v>-2.657799733037987</v>
+        <v>-2.688690338357839</v>
       </c>
     </row>
     <row r="373">
@@ -3419,7 +3419,7 @@
         <v>45117</v>
       </c>
       <c r="B373" t="n">
-        <v>-2.659892391483328</v>
+        <v>-2.660268983385337</v>
       </c>
     </row>
     <row r="374">
@@ -3427,7 +3427,7 @@
         <v>45118</v>
       </c>
       <c r="B374" t="n">
-        <v>-2.667125715269715</v>
+        <v>-2.666221842332502</v>
       </c>
     </row>
     <row r="375">
@@ -3435,7 +3435,7 @@
         <v>45119</v>
       </c>
       <c r="B375" t="n">
-        <v>-2.674511570299807</v>
+        <v>-2.679813975632032</v>
       </c>
     </row>
     <row r="376">
@@ -3443,7 +3443,7 @@
         <v>45120</v>
       </c>
       <c r="B376" t="n">
-        <v>-2.716665047355897</v>
+        <v>-2.743062100217635</v>
       </c>
     </row>
     <row r="377">
@@ -3451,4559 +3451,4599 @@
         <v>45121</v>
       </c>
       <c r="B377" t="n">
-        <v>-2.706494945245242</v>
+        <v>-2.712171418227975</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="n">
-        <v>45125</v>
+        <v>45124</v>
       </c>
       <c r="B378" t="n">
-        <v>-2.729935708817113</v>
+        <v>-2.701190462683466</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="n">
-        <v>45126</v>
+        <v>45125</v>
       </c>
       <c r="B379" t="n">
-        <v>-2.730920039782402</v>
+        <v>-2.724366411414777</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="n">
-        <v>45127</v>
+        <v>45126</v>
       </c>
       <c r="B380" t="n">
-        <v>-2.684845697547177</v>
+        <v>-2.725575578678378</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="n">
-        <v>45128</v>
+        <v>45127</v>
       </c>
       <c r="B381" t="n">
-        <v>-2.657263191914138</v>
+        <v>-2.675259983735722</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="n">
-        <v>45131</v>
+        <v>45128</v>
       </c>
       <c r="B382" t="n">
-        <v>-2.699069554586372</v>
+        <v>-2.651628619008517</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="n">
-        <v>45132</v>
+        <v>45131</v>
       </c>
       <c r="B383" t="n">
-        <v>-2.905710975920766</v>
+        <v>-2.694155820303743</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="n">
-        <v>45133</v>
+        <v>45132</v>
       </c>
       <c r="B384" t="n">
-        <v>-2.849291264149862</v>
+        <v>-2.891327002427994</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="n">
-        <v>45134</v>
+        <v>45133</v>
       </c>
       <c r="B385" t="n">
-        <v>-2.847641204973575</v>
+        <v>-2.838165044095291</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="n">
-        <v>45135</v>
+        <v>45134</v>
       </c>
       <c r="B386" t="n">
-        <v>-2.871033999675936</v>
+        <v>-2.836589900047862</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="n">
-        <v>45138</v>
+        <v>45135</v>
       </c>
       <c r="B387" t="n">
-        <v>-2.819061171856078</v>
+        <v>-2.860773387818811</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="n">
-        <v>45139</v>
+        <v>45138</v>
       </c>
       <c r="B388" t="n">
-        <v>-2.819106964735756</v>
+        <v>-2.806903266602017</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="n">
-        <v>45140</v>
+        <v>45139</v>
       </c>
       <c r="B389" t="n">
-        <v>-2.920871269012028</v>
+        <v>-2.806562138831432</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="n">
-        <v>45141</v>
+        <v>45140</v>
       </c>
       <c r="B390" t="n">
-        <v>-2.823029275037368</v>
+        <v>-2.916960149008544</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="n">
-        <v>45142</v>
+        <v>45141</v>
       </c>
       <c r="B391" t="n">
-        <v>-2.771897007837892</v>
+        <v>-2.92045109415831</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="n">
-        <v>45145</v>
+        <v>45142</v>
       </c>
       <c r="B392" t="n">
-        <v>-2.772015508738839</v>
+        <v>-2.826047511386845</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="n">
-        <v>45146</v>
+        <v>45145</v>
       </c>
       <c r="B393" t="n">
-        <v>-2.789442150212058</v>
+        <v>-2.767867220309825</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="n">
-        <v>45147</v>
+        <v>45146</v>
       </c>
       <c r="B394" t="n">
-        <v>-2.789774750560255</v>
+        <v>-2.808866324458847</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="n">
-        <v>45148</v>
+        <v>45147</v>
       </c>
       <c r="B395" t="n">
-        <v>-2.78844440377354</v>
+        <v>-2.790566679018358</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="n">
-        <v>45149</v>
+        <v>45148</v>
       </c>
       <c r="B396" t="n">
-        <v>-2.797154302335481</v>
+        <v>-2.790702488825155</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="n">
-        <v>45152</v>
+        <v>45149</v>
       </c>
       <c r="B397" t="n">
-        <v>-2.834907759244793</v>
+        <v>-2.79765674767948</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="n">
-        <v>45153</v>
+        <v>45152</v>
       </c>
       <c r="B398" t="n">
-        <v>-2.844334487929713</v>
+        <v>-2.833948553558808</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="n">
-        <v>45154</v>
+        <v>45153</v>
       </c>
       <c r="B399" t="n">
-        <v>-2.843406183522012</v>
+        <v>-2.848274457747181</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="n">
-        <v>45155</v>
+        <v>45154</v>
       </c>
       <c r="B400" t="n">
-        <v>-2.839319155949931</v>
+        <v>-2.875902252711579</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="n">
-        <v>45156</v>
+        <v>45155</v>
       </c>
       <c r="B401" t="n">
-        <v>-2.897544835187462</v>
+        <v>-2.871840209922556</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="n">
-        <v>45159</v>
+        <v>45156</v>
       </c>
       <c r="B402" t="n">
-        <v>-2.928310828369712</v>
+        <v>-2.914955754880686</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="n">
-        <v>45160</v>
+        <v>45159</v>
       </c>
       <c r="B403" t="n">
-        <v>-2.856632122480153</v>
+        <v>-2.969033657491708</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="n">
-        <v>45161</v>
+        <v>45160</v>
       </c>
       <c r="B404" t="n">
-        <v>-2.803976660407979</v>
+        <v>-2.977669487259872</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="n">
-        <v>45162</v>
+        <v>45161</v>
       </c>
       <c r="B405" t="n">
-        <v>-2.828688211133194</v>
+        <v>-2.95277410874431</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="n">
-        <v>45163</v>
+        <v>45162</v>
       </c>
       <c r="B406" t="n">
-        <v>-2.845637554342746</v>
+        <v>-2.924007286692654</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="n">
-        <v>45166</v>
+        <v>45163</v>
       </c>
       <c r="B407" t="n">
-        <v>-2.830610853193079</v>
+        <v>-2.890842475016003</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="n">
-        <v>45167</v>
+        <v>45166</v>
       </c>
       <c r="B408" t="n">
-        <v>-2.803036873269726</v>
+        <v>-2.869945428956439</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="n">
-        <v>45168</v>
+        <v>45167</v>
       </c>
       <c r="B409" t="n">
-        <v>-2.709666621520542</v>
+        <v>-2.923974751292224</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="n">
-        <v>45169</v>
+        <v>45168</v>
       </c>
       <c r="B410" t="n">
-        <v>-2.704533300783406</v>
+        <v>-2.892456619042271</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="n">
-        <v>45173</v>
+        <v>45169</v>
       </c>
       <c r="B411" t="n">
-        <v>-2.782979832154079</v>
+        <v>-2.807446681214871</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="n">
-        <v>45174</v>
+        <v>45170</v>
       </c>
       <c r="B412" t="n">
-        <v>-2.803614195815878</v>
+        <v>-2.713204570404952</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="n">
-        <v>45175</v>
+        <v>45173</v>
       </c>
       <c r="B413" t="n">
-        <v>-2.803251641943789</v>
+        <v>-2.786551775669201</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="n">
-        <v>45176</v>
+        <v>45174</v>
       </c>
       <c r="B414" t="n">
-        <v>-2.817089018101354</v>
+        <v>-2.846666267999293</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="n">
-        <v>45180</v>
+        <v>45175</v>
       </c>
       <c r="B415" t="n">
-        <v>-2.795785155834509</v>
+        <v>-2.807000776571207</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="n">
-        <v>45181</v>
+        <v>45176</v>
       </c>
       <c r="B416" t="n">
-        <v>-2.761557437885674</v>
+        <v>-2.827330221175377</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="n">
-        <v>45182</v>
+        <v>45177</v>
       </c>
       <c r="B417" t="n">
-        <v>-2.699137069196485</v>
+        <v>-2.817769324048152</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="n">
-        <v>45183</v>
+        <v>45180</v>
       </c>
       <c r="B418" t="n">
-        <v>-2.691753725437948</v>
+        <v>-2.798296296596579</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="n">
-        <v>45184</v>
+        <v>45181</v>
       </c>
       <c r="B419" t="n">
-        <v>-2.689387102360198</v>
+        <v>-2.763882879124307</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="n">
-        <v>45187</v>
+        <v>45182</v>
       </c>
       <c r="B420" t="n">
-        <v>-2.7107388221381</v>
+        <v>-2.703868529573306</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="n">
-        <v>45188</v>
+        <v>45183</v>
       </c>
       <c r="B421" t="n">
-        <v>-2.642967154702374</v>
+        <v>-2.695174202471334</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="n">
-        <v>45189</v>
+        <v>45184</v>
       </c>
       <c r="B422" t="n">
-        <v>-2.641515238733656</v>
+        <v>-2.692786725854991</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="n">
-        <v>45190</v>
+        <v>45187</v>
       </c>
       <c r="B423" t="n">
-        <v>-2.647419410283864</v>
+        <v>-2.714275381818406</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="n">
-        <v>45191</v>
+        <v>45188</v>
       </c>
       <c r="B424" t="n">
-        <v>-2.697465412949835</v>
+        <v>-2.645470954385984</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="n">
-        <v>45194</v>
+        <v>45189</v>
       </c>
       <c r="B425" t="n">
-        <v>-2.741377386334476</v>
+        <v>-2.645129926620074</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="n">
-        <v>45195</v>
+        <v>45190</v>
       </c>
       <c r="B426" t="n">
-        <v>-2.709294862310791</v>
+        <v>-2.649217953648304</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="n">
-        <v>45196</v>
+        <v>45191</v>
       </c>
       <c r="B427" t="n">
-        <v>-2.617659806068861</v>
+        <v>-2.696735331678045</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="n">
-        <v>45197</v>
+        <v>45194</v>
       </c>
       <c r="B428" t="n">
-        <v>-2.604659902677211</v>
+        <v>-2.739169932433106</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="n">
-        <v>45198</v>
+        <v>45195</v>
       </c>
       <c r="B429" t="n">
-        <v>-2.660741062757627</v>
+        <v>-2.705920505754394</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="n">
-        <v>45202</v>
+        <v>45196</v>
       </c>
       <c r="B430" t="n">
-        <v>-2.736801212241121</v>
+        <v>-2.616243290264364</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="n">
-        <v>45203</v>
+        <v>45197</v>
       </c>
       <c r="B431" t="n">
-        <v>-2.676301245396366</v>
+        <v>-2.60439208152508</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="n">
-        <v>45204</v>
+        <v>45198</v>
       </c>
       <c r="B432" t="n">
-        <v>-2.643980746675173</v>
+        <v>-2.660474375667109</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="n">
-        <v>45205</v>
+        <v>45202</v>
       </c>
       <c r="B433" t="n">
-        <v>-2.641904736889706</v>
+        <v>-2.736544723291983</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="n">
-        <v>45208</v>
+        <v>45203</v>
       </c>
       <c r="B434" t="n">
-        <v>-2.638720623441626</v>
+        <v>-2.675219082613032</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="n">
-        <v>45209</v>
+        <v>45204</v>
       </c>
       <c r="B435" t="n">
-        <v>-2.64526071468351</v>
+        <v>-2.644908844715298</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="n">
-        <v>45210</v>
+        <v>45205</v>
       </c>
       <c r="B436" t="n">
-        <v>-2.625977814208354</v>
+        <v>-2.642797217513513</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="n">
-        <v>45211</v>
+        <v>45208</v>
       </c>
       <c r="B437" t="n">
-        <v>-2.632589895041189</v>
+        <v>-2.639268025516676</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="n">
-        <v>45212</v>
+        <v>45209</v>
       </c>
       <c r="B438" t="n">
-        <v>-2.686547503509501</v>
+        <v>-2.645811501684026</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="n">
-        <v>45215</v>
+        <v>45210</v>
       </c>
       <c r="B439" t="n">
-        <v>-2.556922098787046</v>
+        <v>-2.62825593410258</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="n">
-        <v>45216</v>
+        <v>45211</v>
       </c>
       <c r="B440" t="n">
-        <v>-2.545336029840005</v>
+        <v>-2.63492414577516</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="n">
-        <v>45217</v>
+        <v>45212</v>
       </c>
       <c r="B441" t="n">
-        <v>-2.509564359736793</v>
+        <v>-2.686507893944069</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="n">
-        <v>45218</v>
+        <v>45215</v>
       </c>
       <c r="B442" t="n">
-        <v>-2.534739297553017</v>
+        <v>-2.561243670796159</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="n">
-        <v>45219</v>
+        <v>45216</v>
       </c>
       <c r="B443" t="n">
-        <v>-2.538073347183515</v>
+        <v>-2.549551770525683</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="n">
-        <v>45223</v>
+        <v>45217</v>
       </c>
       <c r="B444" t="n">
-        <v>-2.546326983969912</v>
+        <v>-2.513468286564344</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="n">
-        <v>45224</v>
+        <v>45218</v>
       </c>
       <c r="B445" t="n">
-        <v>-2.541782415993175</v>
+        <v>-2.538859646947113</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="n">
-        <v>45225</v>
+        <v>45219</v>
       </c>
       <c r="B446" t="n">
-        <v>-2.511413747468754</v>
+        <v>-2.541587712861661</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="n">
-        <v>45226</v>
+        <v>45223</v>
       </c>
       <c r="B447" t="n">
-        <v>-2.547692618730857</v>
+        <v>-2.550869885766794</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="n">
-        <v>45229</v>
+        <v>45224</v>
       </c>
       <c r="B448" t="n">
-        <v>-2.623524258576216</v>
+        <v>-2.545864358442115</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="n">
-        <v>45230</v>
+        <v>45225</v>
       </c>
       <c r="B449" t="n">
-        <v>-2.609611881698009</v>
+        <v>-2.512779886378588</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="n">
-        <v>45231</v>
+        <v>45226</v>
       </c>
       <c r="B450" t="n">
-        <v>-2.608763442301633</v>
+        <v>-2.550254014748188</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="n">
-        <v>45232</v>
+        <v>45229</v>
       </c>
       <c r="B451" t="n">
-        <v>-2.599607356604472</v>
+        <v>-2.626408919042919</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="n">
-        <v>45233</v>
+        <v>45230</v>
       </c>
       <c r="B452" t="n">
-        <v>-2.645808589328437</v>
+        <v>-2.613364354406218</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="n">
-        <v>45236</v>
+        <v>45231</v>
       </c>
       <c r="B453" t="n">
-        <v>-2.638394245408425</v>
+        <v>-2.612510027109421</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="n">
-        <v>45237</v>
+        <v>45232</v>
       </c>
       <c r="B454" t="n">
-        <v>-2.662180471679639</v>
+        <v>-2.603291094242857</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="n">
-        <v>45238</v>
+        <v>45233</v>
       </c>
       <c r="B455" t="n">
-        <v>-2.660378155736848</v>
+        <v>-2.649822825819536</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="n">
-        <v>45239</v>
+        <v>45236</v>
       </c>
       <c r="B456" t="n">
-        <v>-2.66050948841804</v>
+        <v>-2.640439617634156</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="n">
-        <v>45240</v>
+        <v>45237</v>
       </c>
       <c r="B457" t="n">
-        <v>-2.692702916348998</v>
+        <v>-2.664346798680556</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="n">
-        <v>45243</v>
+        <v>45238</v>
       </c>
       <c r="B458" t="n">
-        <v>-2.703570817737118</v>
+        <v>-2.662895377249618</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="n">
-        <v>45244</v>
+        <v>45239</v>
       </c>
       <c r="B459" t="n">
-        <v>-2.694683039183769</v>
+        <v>-2.662989599264546</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="n">
-        <v>45245</v>
+        <v>45240</v>
       </c>
       <c r="B460" t="n">
-        <v>-2.868777861702858</v>
+        <v>-2.692854498554384</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="n">
-        <v>45246</v>
+        <v>45243</v>
       </c>
       <c r="B461" t="n">
-        <v>-2.808975082252581</v>
+        <v>-2.703719849855992</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="n">
-        <v>45247</v>
+        <v>45244</v>
       </c>
       <c r="B462" t="n">
-        <v>-2.858634320722593</v>
+        <v>-2.694834818445795</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="n">
-        <v>45250</v>
+        <v>45245</v>
       </c>
       <c r="B463" t="n">
-        <v>-2.904022400155941</v>
+        <v>-2.860509023475787</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="n">
-        <v>45251</v>
+        <v>45246</v>
       </c>
       <c r="B464" t="n">
-        <v>-2.894286205704872</v>
+        <v>-2.805681504772724</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="n">
-        <v>45252</v>
+        <v>45247</v>
       </c>
       <c r="B465" t="n">
-        <v>-2.894433030194516</v>
+        <v>-2.855047208082831</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="n">
-        <v>45253</v>
+        <v>45250</v>
       </c>
       <c r="B466" t="n">
-        <v>-2.859809563756673</v>
+        <v>-2.90013400225632</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="n">
-        <v>45254</v>
+        <v>45251</v>
       </c>
       <c r="B467" t="n">
-        <v>-2.873729755804081</v>
+        <v>-2.892045650839391</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="n">
-        <v>45257</v>
+        <v>45252</v>
       </c>
       <c r="B468" t="n">
-        <v>-2.770742798539003</v>
+        <v>-2.892018522350978</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="n">
-        <v>45258</v>
+        <v>45253</v>
       </c>
       <c r="B469" t="n">
-        <v>-2.782107072196576</v>
+        <v>-2.856919763463301</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="n">
-        <v>45259</v>
+        <v>45254</v>
       </c>
       <c r="B470" t="n">
-        <v>-2.814742901411452</v>
+        <v>-2.876043142055829</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="n">
-        <v>45260</v>
+        <v>45257</v>
       </c>
       <c r="B471" t="n">
-        <v>-2.806911567265268</v>
+        <v>-2.768315824686282</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="n">
-        <v>45261</v>
+        <v>45258</v>
       </c>
       <c r="B472" t="n">
-        <v>-2.830001699917817</v>
+        <v>-2.779617948837537</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="n">
-        <v>45264</v>
+        <v>45259</v>
       </c>
       <c r="B473" t="n">
-        <v>-2.836341461041262</v>
+        <v>-2.812067213295754</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="n">
-        <v>45265</v>
+        <v>45260</v>
       </c>
       <c r="B474" t="n">
-        <v>-2.839083361458858</v>
+        <v>-2.80288781426169</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="2" t="n">
-        <v>45266</v>
+        <v>45261</v>
       </c>
       <c r="B475" t="n">
-        <v>-2.847997384977083</v>
+        <v>-2.825774614588236</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="n">
-        <v>45267</v>
+        <v>45264</v>
       </c>
       <c r="B476" t="n">
-        <v>-2.851313845129277</v>
+        <v>-2.833441110706556</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="n">
-        <v>45268</v>
+        <v>45265</v>
       </c>
       <c r="B477" t="n">
-        <v>-2.827187871345632</v>
+        <v>-2.836165673374929</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="n">
-        <v>45271</v>
+        <v>45266</v>
       </c>
       <c r="B478" t="n">
-        <v>-2.83360512377097</v>
+        <v>-2.845021961158873</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="n">
-        <v>45272</v>
+        <v>45267</v>
       </c>
       <c r="B479" t="n">
-        <v>-2.849296153423305</v>
+        <v>-2.848316718109319</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="n">
-        <v>45273</v>
+        <v>45268</v>
       </c>
       <c r="B480" t="n">
-        <v>-2.783933172435235</v>
+        <v>-2.824398210920277</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="n">
-        <v>45274</v>
+        <v>45271</v>
       </c>
       <c r="B481" t="n">
-        <v>-2.639261202087478</v>
+        <v>-2.829446259927981</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="n">
-        <v>45275</v>
+        <v>45272</v>
       </c>
       <c r="B482" t="n">
-        <v>-2.69580957180077</v>
+        <v>-2.84499565345778</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="n">
-        <v>45278</v>
+        <v>45273</v>
       </c>
       <c r="B483" t="n">
-        <v>-2.704712796267041</v>
+        <v>-2.780195338686376</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="n">
-        <v>45279</v>
+        <v>45274</v>
       </c>
       <c r="B484" t="n">
-        <v>-2.661242468206133</v>
+        <v>-2.630665057176372</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="n">
-        <v>45280</v>
+        <v>45275</v>
       </c>
       <c r="B485" t="n">
-        <v>-2.611055222707299</v>
+        <v>-2.681370011366362</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="n">
-        <v>45281</v>
+        <v>45278</v>
       </c>
       <c r="B486" t="n">
-        <v>-2.499150122273469</v>
+        <v>-2.690012606960015</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="n">
-        <v>45282</v>
+        <v>45279</v>
       </c>
       <c r="B487" t="n">
-        <v>-2.497884965527308</v>
+        <v>-2.647776846409306</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="2" t="n">
-        <v>45287</v>
+        <v>45280</v>
       </c>
       <c r="B488" t="n">
-        <v>-2.502875314986948</v>
+        <v>-2.598019351802458</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="n">
-        <v>45288</v>
+        <v>45281</v>
       </c>
       <c r="B489" t="n">
-        <v>-2.55540082716295</v>
+        <v>-2.488840969038979</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="n">
-        <v>45289</v>
+        <v>45282</v>
       </c>
       <c r="B490" t="n">
-        <v>-2.50670607778059</v>
+        <v>-2.490836442192467</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="n">
-        <v>45293</v>
+        <v>45287</v>
       </c>
       <c r="B491" t="n">
-        <v>-2.508138048391655</v>
+        <v>-2.495759315106277</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="n">
-        <v>45294</v>
+        <v>45288</v>
       </c>
       <c r="B492" t="n">
-        <v>-2.509951280371593</v>
+        <v>-2.550134612707367</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="n">
-        <v>45295</v>
+        <v>45289</v>
       </c>
       <c r="B493" t="n">
-        <v>-2.509129292441297</v>
+        <v>-2.501897065045597</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="n">
-        <v>45296</v>
+        <v>45293</v>
       </c>
       <c r="B494" t="n">
-        <v>-2.514409037295413</v>
+        <v>-2.504606657271059</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="n">
-        <v>45299</v>
+        <v>45294</v>
       </c>
       <c r="B495" t="n">
-        <v>-2.43459320963535</v>
+        <v>-2.506147129063729</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="n">
-        <v>45300</v>
+        <v>45295</v>
       </c>
       <c r="B496" t="n">
-        <v>-2.433482285849937</v>
+        <v>-2.504306408149688</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="2" t="n">
-        <v>45301</v>
+        <v>45296</v>
       </c>
       <c r="B497" t="n">
-        <v>-2.424493895204601</v>
+        <v>-2.508560558610931</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="n">
-        <v>45302</v>
+        <v>45299</v>
       </c>
       <c r="B498" t="n">
-        <v>-2.430810565583506</v>
+        <v>-2.419908434386609</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="n">
-        <v>45303</v>
+        <v>45300</v>
       </c>
       <c r="B499" t="n">
-        <v>-2.425506702778614</v>
+        <v>-2.418470892657094</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="n">
-        <v>45306</v>
+        <v>45301</v>
       </c>
       <c r="B500" t="n">
-        <v>-2.424317315768932</v>
+        <v>-2.410725792114229</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="n">
-        <v>45307</v>
+        <v>45302</v>
       </c>
       <c r="B501" t="n">
-        <v>-2.421053134595338</v>
+        <v>-2.416195337469093</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="2" t="n">
-        <v>45308</v>
+        <v>45303</v>
       </c>
       <c r="B502" t="n">
-        <v>-2.507052949337767</v>
+        <v>-2.411038869204258</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" s="2" t="n">
-        <v>45309</v>
+        <v>45306</v>
       </c>
       <c r="B503" t="n">
-        <v>-2.509181836911357</v>
+        <v>-2.410194706780998</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="2" t="n">
-        <v>45310</v>
+        <v>45307</v>
       </c>
       <c r="B504" t="n">
-        <v>-2.491850183996438</v>
+        <v>-2.403183443791635</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="2" t="n">
-        <v>45313</v>
+        <v>45308</v>
       </c>
       <c r="B505" t="n">
-        <v>-2.508712779456361</v>
+        <v>-2.489515705090416</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="n">
-        <v>45314</v>
+        <v>45309</v>
       </c>
       <c r="B506" t="n">
-        <v>-2.554898275617693</v>
+        <v>-2.49245327360916</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" s="2" t="n">
-        <v>45315</v>
+        <v>45310</v>
       </c>
       <c r="B507" t="n">
-        <v>-2.676462377704582</v>
+        <v>-2.475669460745113</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" s="2" t="n">
-        <v>45316</v>
+        <v>45313</v>
       </c>
       <c r="B508" t="n">
-        <v>-2.702593961366424</v>
+        <v>-2.490591965246388</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" s="2" t="n">
-        <v>45317</v>
+        <v>45314</v>
       </c>
       <c r="B509" t="n">
-        <v>-2.703413741357604</v>
+        <v>-2.534693400050592</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="2" t="n">
-        <v>45320</v>
+        <v>45315</v>
       </c>
       <c r="B510" t="n">
-        <v>-2.709439864968</v>
+        <v>-2.651560375415604</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" s="2" t="n">
-        <v>45321</v>
+        <v>45316</v>
       </c>
       <c r="B511" t="n">
-        <v>-2.781286861239272</v>
+        <v>-2.671375951955969</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" s="2" t="n">
-        <v>45322</v>
+        <v>45317</v>
       </c>
       <c r="B512" t="n">
-        <v>-2.807258125455123</v>
+        <v>-2.667242218165816</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" s="2" t="n">
-        <v>45323</v>
+        <v>45320</v>
       </c>
       <c r="B513" t="n">
-        <v>-2.723559156009005</v>
+        <v>-2.673047075608562</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" s="2" t="n">
-        <v>45324</v>
+        <v>45321</v>
       </c>
       <c r="B514" t="n">
-        <v>-2.687725940670946</v>
+        <v>-2.739543698605159</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" s="2" t="n">
-        <v>45327</v>
+        <v>45322</v>
       </c>
       <c r="B515" t="n">
-        <v>-2.675098748985228</v>
+        <v>-2.761203595790033</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" s="2" t="n">
-        <v>45328</v>
+        <v>45323</v>
       </c>
       <c r="B516" t="n">
-        <v>-2.856790369132234</v>
+        <v>-2.68575369587215</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" s="2" t="n">
-        <v>45329</v>
+        <v>45324</v>
       </c>
       <c r="B517" t="n">
-        <v>-2.831422574593984</v>
+        <v>-2.65380359772456</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" s="2" t="n">
-        <v>45330</v>
+        <v>45327</v>
       </c>
       <c r="B518" t="n">
-        <v>-2.728197070255304</v>
+        <v>-2.642310253533717</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" s="2" t="n">
-        <v>45331</v>
+        <v>45328</v>
       </c>
       <c r="B519" t="n">
-        <v>-2.736019203704581</v>
+        <v>-2.830237415959765</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" s="2" t="n">
-        <v>45336</v>
+        <v>45329</v>
       </c>
       <c r="B520" t="n">
-        <v>-2.739011661956456</v>
+        <v>-2.806945368500583</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" s="2" t="n">
-        <v>45337</v>
+        <v>45330</v>
       </c>
       <c r="B521" t="n">
-        <v>-2.719900542594151</v>
+        <v>-2.7064823570016</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" s="2" t="n">
-        <v>45338</v>
+        <v>45331</v>
       </c>
       <c r="B522" t="n">
-        <v>-2.794454866666592</v>
+        <v>-2.715220318823143</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" s="2" t="n">
-        <v>45341</v>
+        <v>45336</v>
       </c>
       <c r="B523" t="n">
-        <v>-2.790598735648733</v>
+        <v>-2.718092718665525</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" s="2" t="n">
-        <v>45342</v>
+        <v>45337</v>
       </c>
       <c r="B524" t="n">
-        <v>-2.794010964635799</v>
+        <v>-2.700906945978899</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="2" t="n">
-        <v>45343</v>
+        <v>45338</v>
       </c>
       <c r="B525" t="n">
-        <v>-2.77915920145633</v>
+        <v>-2.780630917324997</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" s="2" t="n">
-        <v>45344</v>
+        <v>45341</v>
       </c>
       <c r="B526" t="n">
-        <v>-2.747497814217136</v>
+        <v>-2.781781255807049</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" s="2" t="n">
-        <v>45345</v>
+        <v>45342</v>
       </c>
       <c r="B527" t="n">
-        <v>-2.747275640082774</v>
+        <v>-2.785567606370909</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" s="2" t="n">
-        <v>45348</v>
+        <v>45343</v>
       </c>
       <c r="B528" t="n">
-        <v>-2.743077645687432</v>
+        <v>-2.771010204253006</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" s="2" t="n">
-        <v>45349</v>
+        <v>45344</v>
       </c>
       <c r="B529" t="n">
-        <v>-2.732648698972917</v>
+        <v>-2.737275015081804</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" s="2" t="n">
-        <v>45350</v>
+        <v>45345</v>
       </c>
       <c r="B530" t="n">
-        <v>-2.753051316245072</v>
+        <v>-2.737558130935068</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" s="2" t="n">
-        <v>45351</v>
+        <v>45348</v>
       </c>
       <c r="B531" t="n">
-        <v>-2.686933719283529</v>
+        <v>-2.731815994034966</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" s="2" t="n">
-        <v>45352</v>
+        <v>45349</v>
       </c>
       <c r="B532" t="n">
-        <v>-2.67388425506669</v>
+        <v>-2.726417818424176</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" s="2" t="n">
-        <v>45355</v>
+        <v>45350</v>
       </c>
       <c r="B533" t="n">
-        <v>-2.674025196416727</v>
+        <v>-2.752336833617796</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" s="2" t="n">
-        <v>45356</v>
+        <v>45351</v>
       </c>
       <c r="B534" t="n">
-        <v>-2.754451998188994</v>
+        <v>-2.689150294517276</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" s="2" t="n">
-        <v>45357</v>
+        <v>45352</v>
       </c>
       <c r="B535" t="n">
-        <v>-2.79264816258172</v>
+        <v>-2.676036054134665</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" s="2" t="n">
-        <v>45358</v>
+        <v>45355</v>
       </c>
       <c r="B536" t="n">
-        <v>-2.766062780521124</v>
+        <v>-2.676186881137919</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" s="2" t="n">
-        <v>45359</v>
+        <v>45356</v>
       </c>
       <c r="B537" t="n">
-        <v>-2.772913652140115</v>
+        <v>-2.75692622950035</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" s="2" t="n">
-        <v>45362</v>
+        <v>45357</v>
       </c>
       <c r="B538" t="n">
-        <v>-2.738861885794352</v>
+        <v>-2.794376782291784</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" s="2" t="n">
-        <v>45363</v>
+        <v>45358</v>
       </c>
       <c r="B539" t="n">
-        <v>-2.860531625098061</v>
+        <v>-2.767734671396572</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" s="2" t="n">
-        <v>45364</v>
+        <v>45359</v>
       </c>
       <c r="B540" t="n">
-        <v>-2.799051577422098</v>
+        <v>-2.775887029369951</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" s="2" t="n">
-        <v>45365</v>
+        <v>45362</v>
       </c>
       <c r="B541" t="n">
-        <v>-2.809311244849788</v>
+        <v>-2.74165787329056</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" s="2" t="n">
-        <v>45366</v>
+        <v>45363</v>
       </c>
       <c r="B542" t="n">
-        <v>-2.823225947850992</v>
+        <v>-2.861714254510469</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" s="2" t="n">
-        <v>45369</v>
+        <v>45364</v>
       </c>
       <c r="B543" t="n">
-        <v>-2.810343768501259</v>
+        <v>-2.804995711289505</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" s="2" t="n">
-        <v>45370</v>
+        <v>45365</v>
       </c>
       <c r="B544" t="n">
-        <v>-2.804983306270497</v>
+        <v>-2.815385505257447</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" s="2" t="n">
-        <v>45371</v>
+        <v>45366</v>
       </c>
       <c r="B545" t="n">
-        <v>-2.74663436694855</v>
+        <v>-2.827267011044306</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" s="2" t="n">
-        <v>45372</v>
+        <v>45369</v>
       </c>
       <c r="B546" t="n">
-        <v>-2.736988549161013</v>
+        <v>-2.814144325781017</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" s="2" t="n">
-        <v>45373</v>
+        <v>45370</v>
       </c>
       <c r="B547" t="n">
-        <v>-2.796545062648283</v>
+        <v>-2.806682002858282</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" s="2" t="n">
-        <v>45376</v>
+        <v>45371</v>
       </c>
       <c r="B548" t="n">
-        <v>-2.735709270860734</v>
+        <v>-2.75119080854325</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" s="2" t="n">
-        <v>45377</v>
+        <v>45372</v>
       </c>
       <c r="B549" t="n">
-        <v>-2.743840460164814</v>
+        <v>-2.741398465526276</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" s="2" t="n">
-        <v>45378</v>
+        <v>45373</v>
       </c>
       <c r="B550" t="n">
-        <v>-2.767060601499623</v>
+        <v>-2.807010478676081</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" s="2" t="n">
-        <v>45379</v>
+        <v>45376</v>
       </c>
       <c r="B551" t="n">
-        <v>-2.696281824313399</v>
+        <v>-2.744931873823814</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" s="2" t="n">
-        <v>45384</v>
+        <v>45377</v>
       </c>
       <c r="B552" t="n">
-        <v>-2.74245007129787</v>
+        <v>-2.753614722601092</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" s="2" t="n">
-        <v>45385</v>
+        <v>45378</v>
       </c>
       <c r="B553" t="n">
-        <v>-2.75590928066549</v>
+        <v>-2.775230847118758</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" s="2" t="n">
-        <v>45387</v>
+        <v>45379</v>
       </c>
       <c r="B554" t="n">
-        <v>-2.751223497865613</v>
+        <v>-2.70170830127207</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" s="2" t="n">
-        <v>45390</v>
+        <v>45384</v>
       </c>
       <c r="B555" t="n">
-        <v>-2.742942391835098</v>
+        <v>-2.744965303432343</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" s="2" t="n">
-        <v>45391</v>
+        <v>45385</v>
       </c>
       <c r="B556" t="n">
-        <v>-2.722885873084475</v>
+        <v>-2.758501618932347</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" s="2" t="n">
-        <v>45392</v>
+        <v>45387</v>
       </c>
       <c r="B557" t="n">
-        <v>-2.696857796892038</v>
+        <v>-2.753359464810805</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" s="2" t="n">
-        <v>45393</v>
+        <v>45390</v>
       </c>
       <c r="B558" t="n">
-        <v>-2.691089257032469</v>
+        <v>-2.745693492439743</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" s="2" t="n">
-        <v>45394</v>
+        <v>45391</v>
       </c>
       <c r="B559" t="n">
-        <v>-2.743644163458087</v>
+        <v>-2.72724605816755</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" s="2" t="n">
-        <v>45397</v>
+        <v>45392</v>
       </c>
       <c r="B560" t="n">
-        <v>-2.722831037968521</v>
+        <v>-2.699537758204648</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" s="2" t="n">
-        <v>45398</v>
+        <v>45393</v>
       </c>
       <c r="B561" t="n">
-        <v>-2.763265491983549</v>
+        <v>-2.693734396544762</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" s="2" t="n">
-        <v>45399</v>
+        <v>45394</v>
       </c>
       <c r="B562" t="n">
-        <v>-2.760105726018235</v>
+        <v>-2.746845556808397</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" s="2" t="n">
-        <v>45400</v>
+        <v>45397</v>
       </c>
       <c r="B563" t="n">
-        <v>-2.707362375054099</v>
+        <v>-2.727667419161578</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" s="2" t="n">
-        <v>45401</v>
+        <v>45398</v>
       </c>
       <c r="B564" t="n">
-        <v>-2.717912182981867</v>
+        <v>-2.763920115265192</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" s="2" t="n">
-        <v>45404</v>
+        <v>45399</v>
       </c>
       <c r="B565" t="n">
-        <v>-2.709098037854389</v>
+        <v>-2.761364553728646</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" s="2" t="n">
-        <v>45405</v>
+        <v>45400</v>
       </c>
       <c r="B566" t="n">
-        <v>-2.744923876917601</v>
+        <v>-2.70576299958571</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" s="2" t="n">
-        <v>45406</v>
+        <v>45401</v>
       </c>
       <c r="B567" t="n">
-        <v>-2.785878420930838</v>
+        <v>-2.716310409598777</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" s="2" t="n">
-        <v>45407</v>
+        <v>45404</v>
       </c>
       <c r="B568" t="n">
-        <v>-2.788640903561131</v>
+        <v>-2.708470999702234</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" s="2" t="n">
-        <v>45408</v>
+        <v>45405</v>
       </c>
       <c r="B569" t="n">
-        <v>-2.817870234899614</v>
+        <v>-2.741237500577441</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" s="2" t="n">
-        <v>45411</v>
+        <v>45406</v>
       </c>
       <c r="B570" t="n">
-        <v>-2.795477053340929</v>
+        <v>-2.78346789106165</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" s="2" t="n">
-        <v>45412</v>
+        <v>45407</v>
       </c>
       <c r="B571" t="n">
-        <v>-2.786796686666824</v>
+        <v>-2.786073056091216</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" s="2" t="n">
-        <v>45414</v>
+        <v>45408</v>
       </c>
       <c r="B572" t="n">
-        <v>-2.839426722444246</v>
+        <v>-2.815206368606323</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" s="2" t="n">
-        <v>45415</v>
+        <v>45411</v>
       </c>
       <c r="B573" t="n">
-        <v>-2.865471111864417</v>
+        <v>-2.793268543286294</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" s="2" t="n">
-        <v>45418</v>
+        <v>45412</v>
       </c>
       <c r="B574" t="n">
-        <v>-2.871731398863799</v>
+        <v>-2.783424510548641</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" s="2" t="n">
-        <v>45419</v>
+        <v>45414</v>
       </c>
       <c r="B575" t="n">
-        <v>-2.873221419022091</v>
+        <v>-2.835155141241084</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" s="2" t="n">
-        <v>45420</v>
+        <v>45415</v>
       </c>
       <c r="B576" t="n">
-        <v>-2.87883378856891</v>
+        <v>-2.861866602129238</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" s="2" t="n">
-        <v>45421</v>
+        <v>45418</v>
       </c>
       <c r="B577" t="n">
-        <v>-2.901319802155697</v>
+        <v>-2.868263020526672</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" s="2" t="n">
-        <v>45422</v>
+        <v>45419</v>
       </c>
       <c r="B578" t="n">
-        <v>-2.976948468476848</v>
+        <v>-2.870277002014136</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" s="2" t="n">
-        <v>45425</v>
+        <v>45420</v>
       </c>
       <c r="B579" t="n">
-        <v>-2.972231038654682</v>
+        <v>-2.876112775872388</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" s="2" t="n">
-        <v>45426</v>
+        <v>45421</v>
       </c>
       <c r="B580" t="n">
-        <v>-2.953440374663691</v>
+        <v>-2.895784000997492</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" s="2" t="n">
-        <v>45428</v>
+        <v>45422</v>
       </c>
       <c r="B581" t="n">
-        <v>-2.999024371645058</v>
+        <v>-2.973001842440093</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" s="2" t="n">
-        <v>45429</v>
+        <v>45425</v>
       </c>
       <c r="B582" t="n">
-        <v>-3.018207678887745</v>
+        <v>-2.968336173423696</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" s="2" t="n">
-        <v>45432</v>
+        <v>45426</v>
       </c>
       <c r="B583" t="n">
-        <v>-2.882402118266608</v>
+        <v>-2.949256436795704</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" s="2" t="n">
-        <v>45433</v>
+        <v>45428</v>
       </c>
       <c r="B584" t="n">
-        <v>-2.970133269280878</v>
+        <v>-2.99441850594078</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" s="2" t="n">
-        <v>45434</v>
+        <v>45429</v>
       </c>
       <c r="B585" t="n">
-        <v>-2.916661789938784</v>
+        <v>-3.013412660892033</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" s="2" t="n">
-        <v>45435</v>
+        <v>45432</v>
       </c>
       <c r="B586" t="n">
-        <v>-2.967996677180176</v>
+        <v>-2.875700693178644</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" s="2" t="n">
-        <v>45436</v>
+        <v>45433</v>
       </c>
       <c r="B587" t="n">
-        <v>-2.996801977731659</v>
+        <v>-2.965702563273059</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" s="2" t="n">
-        <v>45439</v>
+        <v>45434</v>
       </c>
       <c r="B588" t="n">
-        <v>-3.023153120214471</v>
+        <v>-2.915758783065622</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" s="2" t="n">
-        <v>45440</v>
+        <v>45435</v>
       </c>
       <c r="B589" t="n">
-        <v>-2.958742064124538</v>
+        <v>-2.965607982153783</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" s="2" t="n">
-        <v>45441</v>
+        <v>45436</v>
       </c>
       <c r="B590" t="n">
-        <v>-3.011563323779118</v>
+        <v>-2.993758606364813</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" s="2" t="n">
-        <v>45442</v>
+        <v>45439</v>
       </c>
       <c r="B591" t="n">
-        <v>-3.047976798985119</v>
+        <v>-3.018008520653493</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" s="2" t="n">
-        <v>45443</v>
+        <v>45440</v>
       </c>
       <c r="B592" t="n">
-        <v>-3.033684408975596</v>
+        <v>-2.950781859465253</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" s="2" t="n">
-        <v>45446</v>
+        <v>45441</v>
       </c>
       <c r="B593" t="n">
-        <v>-3.089908289097188</v>
+        <v>-3.002694909910359</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" s="2" t="n">
-        <v>45447</v>
+        <v>45442</v>
       </c>
       <c r="B594" t="n">
-        <v>-3.049398894221182</v>
+        <v>-3.037566460876917</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" s="2" t="n">
-        <v>45448</v>
+        <v>45443</v>
       </c>
       <c r="B595" t="n">
-        <v>-3.032671951078091</v>
+        <v>-3.025539238986626</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" s="2" t="n">
-        <v>45449</v>
+        <v>45446</v>
       </c>
       <c r="B596" t="n">
-        <v>-3.037797602370901</v>
+        <v>-3.085214750180922</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" s="2" t="n">
-        <v>45450</v>
+        <v>45447</v>
       </c>
       <c r="B597" t="n">
-        <v>-3.044771914278741</v>
+        <v>-3.043845572053021</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" s="2" t="n">
-        <v>45454</v>
+        <v>45448</v>
       </c>
       <c r="B598" t="n">
-        <v>-2.973380967454177</v>
+        <v>-3.02268914056604</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" s="2" t="n">
-        <v>45455</v>
+        <v>45449</v>
       </c>
       <c r="B599" t="n">
-        <v>-2.884839724092517</v>
+        <v>-3.028166661005192</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" s="2" t="n">
-        <v>45456</v>
+        <v>45450</v>
       </c>
       <c r="B600" t="n">
-        <v>-2.860682232445159</v>
+        <v>-3.033702871767273</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" s="2" t="n">
-        <v>45457</v>
+        <v>45454</v>
       </c>
       <c r="B601" t="n">
-        <v>-2.842141651396267</v>
+        <v>-2.961247284551847</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" s="2" t="n">
-        <v>45460</v>
+        <v>45455</v>
       </c>
       <c r="B602" t="n">
-        <v>-2.842494024454151</v>
+        <v>-2.878923379629557</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" s="2" t="n">
-        <v>45461</v>
+        <v>45456</v>
       </c>
       <c r="B603" t="n">
-        <v>-2.84183668597896</v>
+        <v>-2.857517229568932</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" s="2" t="n">
-        <v>45462</v>
+        <v>45457</v>
       </c>
       <c r="B604" t="n">
-        <v>-2.900826483526671</v>
+        <v>-2.834114206706723</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" s="2" t="n">
-        <v>45463</v>
+        <v>45460</v>
       </c>
       <c r="B605" t="n">
-        <v>-2.878418758905003</v>
+        <v>-2.834504034132707</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" s="2" t="n">
-        <v>45464</v>
+        <v>45461</v>
       </c>
       <c r="B606" t="n">
-        <v>-2.909007145446244</v>
+        <v>-2.833467481811293</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" s="2" t="n">
-        <v>45467</v>
+        <v>45462</v>
       </c>
       <c r="B607" t="n">
-        <v>-2.897588169974334</v>
+        <v>-2.897256084460873</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" s="2" t="n">
-        <v>45468</v>
+        <v>45463</v>
       </c>
       <c r="B608" t="n">
-        <v>-2.852566701895083</v>
+        <v>-2.873612571022101</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" s="2" t="n">
-        <v>45469</v>
+        <v>45464</v>
       </c>
       <c r="B609" t="n">
-        <v>-2.853477609771447</v>
+        <v>-2.8988848606321</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" s="2" t="n">
-        <v>45470</v>
+        <v>45467</v>
       </c>
       <c r="B610" t="n">
-        <v>-2.867560235043674</v>
+        <v>-2.888960020109962</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" s="2" t="n">
-        <v>45471</v>
+        <v>45468</v>
       </c>
       <c r="B611" t="n">
-        <v>-2.830215950841061</v>
+        <v>-2.842227042411467</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" s="2" t="n">
-        <v>45475</v>
+        <v>45469</v>
       </c>
       <c r="B612" t="n">
-        <v>-2.756991220089112</v>
+        <v>-2.84272798792709</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" s="2" t="n">
-        <v>45476</v>
+        <v>45470</v>
       </c>
       <c r="B613" t="n">
-        <v>-2.769647336104046</v>
+        <v>-2.85413895748395</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" s="2" t="n">
-        <v>45477</v>
+        <v>45471</v>
       </c>
       <c r="B614" t="n">
-        <v>-2.723597703198948</v>
+        <v>-2.815263744207427</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" s="2" t="n">
-        <v>45478</v>
+        <v>45475</v>
       </c>
       <c r="B615" t="n">
-        <v>-2.721060037107703</v>
+        <v>-2.747761564714782</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" s="2" t="n">
-        <v>45481</v>
+        <v>45476</v>
       </c>
       <c r="B616" t="n">
-        <v>-2.729461330703207</v>
+        <v>-2.759345908730155</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" s="2" t="n">
-        <v>45482</v>
+        <v>45477</v>
       </c>
       <c r="B617" t="n">
-        <v>-2.71142040848175</v>
+        <v>-2.719317590170223</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" s="2" t="n">
-        <v>45483</v>
+        <v>45478</v>
       </c>
       <c r="B618" t="n">
-        <v>-2.711733900439854</v>
+        <v>-2.714862745274631</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" s="2" t="n">
-        <v>45484</v>
+        <v>45481</v>
       </c>
       <c r="B619" t="n">
-        <v>-2.739850260564324</v>
+        <v>-2.725200054997239</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" s="2" t="n">
-        <v>45485</v>
+        <v>45482</v>
       </c>
       <c r="B620" t="n">
-        <v>-2.822658033756637</v>
+        <v>-2.705375984363394</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" s="2" t="n">
-        <v>45488</v>
+        <v>45483</v>
       </c>
       <c r="B621" t="n">
-        <v>-2.856099008432125</v>
+        <v>-2.705648875061671</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" s="2" t="n">
-        <v>45489</v>
+        <v>45484</v>
       </c>
       <c r="B622" t="n">
-        <v>-2.889755854447996</v>
+        <v>-2.737826172903495</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" s="2" t="n">
-        <v>45490</v>
+        <v>45485</v>
       </c>
       <c r="B623" t="n">
-        <v>-2.888976601709427</v>
+        <v>-2.81650767049787</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" s="2" t="n">
-        <v>45491</v>
+        <v>45488</v>
       </c>
       <c r="B624" t="n">
-        <v>-2.846012559805359</v>
+        <v>-2.846466956103422</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" s="2" t="n">
-        <v>45492</v>
+        <v>45489</v>
       </c>
       <c r="B625" t="n">
-        <v>-2.894986756902488</v>
+        <v>-2.884903020019141</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" s="2" t="n">
-        <v>45495</v>
+        <v>45490</v>
       </c>
       <c r="B626" t="n">
-        <v>-2.919558425108618</v>
+        <v>-2.884441608536286</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" s="2" t="n">
-        <v>45496</v>
+        <v>45491</v>
       </c>
       <c r="B627" t="n">
-        <v>-2.929618947439173</v>
+        <v>-2.836551496836158</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" s="2" t="n">
-        <v>45497</v>
+        <v>45492</v>
       </c>
       <c r="B628" t="n">
-        <v>-2.903539594519527</v>
+        <v>-2.884086532976374</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" s="2" t="n">
-        <v>45498</v>
+        <v>45495</v>
       </c>
       <c r="B629" t="n">
-        <v>-2.953421392944687</v>
+        <v>-2.910511566990333</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" s="2" t="n">
-        <v>45499</v>
+        <v>45496</v>
       </c>
       <c r="B630" t="n">
-        <v>-2.93803122544835</v>
+        <v>-2.923753600722924</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" s="2" t="n">
-        <v>45502</v>
+        <v>45497</v>
       </c>
       <c r="B631" t="n">
-        <v>-2.975707320889873</v>
+        <v>-2.899128989147266</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" s="2" t="n">
-        <v>45503</v>
+        <v>45498</v>
       </c>
       <c r="B632" t="n">
-        <v>-3.006418150001561</v>
+        <v>-2.952232706094765</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" s="2" t="n">
-        <v>45504</v>
+        <v>45499</v>
       </c>
       <c r="B633" t="n">
-        <v>-3.131315507021331</v>
+        <v>-2.938627102482392</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" s="2" t="n">
-        <v>45505</v>
+        <v>45502</v>
       </c>
       <c r="B634" t="n">
-        <v>-3.09658201046932</v>
+        <v>-2.98322257974211</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" s="2" t="n">
-        <v>45506</v>
+        <v>45503</v>
       </c>
       <c r="B635" t="n">
-        <v>-3.125319348351151</v>
+        <v>-3.020278141007675</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" s="2" t="n">
-        <v>45509</v>
+        <v>45504</v>
       </c>
       <c r="B636" t="n">
-        <v>-3.181733459545649</v>
+        <v>-3.143181364612674</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" s="2" t="n">
-        <v>45510</v>
+        <v>45505</v>
       </c>
       <c r="B637" t="n">
-        <v>-3.152496686533031</v>
+        <v>-3.109242782683399</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" s="2" t="n">
-        <v>45511</v>
+        <v>45506</v>
       </c>
       <c r="B638" t="n">
-        <v>-3.198721551603857</v>
+        <v>-3.131744792066597</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" s="2" t="n">
-        <v>45512</v>
+        <v>45509</v>
       </c>
       <c r="B639" t="n">
-        <v>-3.143731622869305</v>
+        <v>-3.193891206169392</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" s="2" t="n">
-        <v>45513</v>
+        <v>45510</v>
       </c>
       <c r="B640" t="n">
-        <v>-3.187696013623199</v>
+        <v>-3.161491397620535</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" s="2" t="n">
-        <v>45516</v>
+        <v>45511</v>
       </c>
       <c r="B641" t="n">
-        <v>-3.172443073613616</v>
+        <v>-3.21314700031205</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" s="2" t="n">
-        <v>45517</v>
+        <v>45512</v>
       </c>
       <c r="B642" t="n">
-        <v>-3.155892920647989</v>
+        <v>-3.213248642566725</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" s="2" t="n">
-        <v>45518</v>
+        <v>45513</v>
       </c>
       <c r="B643" t="n">
-        <v>-3.143687654503029</v>
+        <v>-3.20209109185681</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" s="2" t="n">
-        <v>45519</v>
+        <v>45516</v>
       </c>
       <c r="B644" t="n">
-        <v>-3.142111862094501</v>
+        <v>-3.197478222097002</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" s="2" t="n">
-        <v>45520</v>
+        <v>45517</v>
       </c>
       <c r="B645" t="n">
-        <v>-3.176376300122379</v>
+        <v>-3.183910621040241</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" s="2" t="n">
-        <v>45523</v>
+        <v>45518</v>
       </c>
       <c r="B646" t="n">
-        <v>-3.092107952260833</v>
+        <v>-3.162519094743785</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" s="2" t="n">
-        <v>45524</v>
+        <v>45519</v>
       </c>
       <c r="B647" t="n">
-        <v>-3.063490059424244</v>
+        <v>-3.148954375657028</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" s="2" t="n">
-        <v>45525</v>
+        <v>45520</v>
       </c>
       <c r="B648" t="n">
-        <v>-3.075482047827688</v>
+        <v>-3.241329730195782</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" s="2" t="n">
-        <v>45526</v>
+        <v>45523</v>
       </c>
       <c r="B649" t="n">
-        <v>-2.816865795679967</v>
+        <v>-3.214130382776087</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" s="2" t="n">
-        <v>45527</v>
+        <v>45524</v>
       </c>
       <c r="B650" t="n">
-        <v>-2.814150719988133</v>
+        <v>-3.107593418608212</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" s="2" t="n">
-        <v>45530</v>
+        <v>45525</v>
       </c>
       <c r="B651" t="n">
-        <v>-2.630707450356913</v>
+        <v>-3.085055571894879</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" s="2" t="n">
-        <v>45531</v>
+        <v>45526</v>
       </c>
       <c r="B652" t="n">
-        <v>-2.541100885430505</v>
+        <v>-3.136992251828924</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" s="2" t="n">
-        <v>45532</v>
+        <v>45527</v>
       </c>
       <c r="B653" t="n">
-        <v>-2.509983122621721</v>
+        <v>-2.820043177239618</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" s="2" t="n">
-        <v>45533</v>
+        <v>45530</v>
       </c>
       <c r="B654" t="n">
-        <v>-2.300960714052043</v>
+        <v>-2.82727227564892</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" s="2" t="n">
-        <v>45534</v>
+        <v>45531</v>
       </c>
       <c r="B655" t="n">
-        <v>-2.299694209900965</v>
+        <v>-2.638053631897194</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" s="2" t="n">
-        <v>45537</v>
+        <v>45532</v>
       </c>
       <c r="B656" t="n">
-        <v>-2.277150020055372</v>
+        <v>-2.55174548045155</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" s="2" t="n">
-        <v>45538</v>
+        <v>45533</v>
       </c>
       <c r="B657" t="n">
-        <v>-2.267471091247055</v>
+        <v>-2.513709579471638</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" s="2" t="n">
-        <v>45539</v>
+        <v>45534</v>
       </c>
       <c r="B658" t="n">
-        <v>-1.96452328469551</v>
+        <v>-2.310796631758927</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" s="2" t="n">
-        <v>45540</v>
+        <v>45537</v>
       </c>
       <c r="B659" t="n">
-        <v>-1.958916175526204</v>
+        <v>-2.31530279908973</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" s="2" t="n">
-        <v>45544</v>
+        <v>45538</v>
       </c>
       <c r="B660" t="n">
-        <v>-1.943385714550008</v>
+        <v>-2.277585349478997</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" s="2" t="n">
-        <v>45545</v>
+        <v>45539</v>
       </c>
       <c r="B661" t="n">
-        <v>-1.942455686726503</v>
+        <v>-2.273511270358425</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" s="2" t="n">
-        <v>45546</v>
+        <v>45540</v>
       </c>
       <c r="B662" t="n">
-        <v>-1.916938721809192</v>
+        <v>-1.964827947122319</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" s="2" t="n">
-        <v>45547</v>
+        <v>45541</v>
       </c>
       <c r="B663" t="n">
-        <v>-1.918384596846601</v>
+        <v>-1.959212243352704</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" s="2" t="n">
-        <v>45548</v>
+        <v>45544</v>
       </c>
       <c r="B664" t="n">
-        <v>-1.916979745222888</v>
+        <v>-1.942361546284319</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" s="2" t="n">
-        <v>45551</v>
+        <v>45545</v>
       </c>
       <c r="B665" t="n">
-        <v>-1.890388859760922</v>
+        <v>-1.941434607469472</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" s="2" t="n">
-        <v>45552</v>
+        <v>45546</v>
       </c>
       <c r="B666" t="n">
-        <v>-1.889548813902478</v>
+        <v>-1.914698668116577</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" s="2" t="n">
-        <v>45554</v>
+        <v>45547</v>
       </c>
       <c r="B667" t="n">
-        <v>-1.898339075637356</v>
+        <v>-1.916454952153976</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" s="2" t="n">
-        <v>45555</v>
+        <v>45548</v>
       </c>
       <c r="B668" t="n">
-        <v>-1.897545778957341</v>
+        <v>-1.91509418134157</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" s="2" t="n">
-        <v>45558</v>
+        <v>45551</v>
       </c>
       <c r="B669" t="n">
-        <v>-1.893740966116559</v>
+        <v>-1.887844770368551</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" s="2" t="n">
-        <v>45559</v>
+        <v>45552</v>
       </c>
       <c r="B670" t="n">
-        <v>-1.931188863797676</v>
+        <v>-1.88671237366608</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" s="2" t="n">
-        <v>45560</v>
+        <v>45554</v>
       </c>
       <c r="B671" t="n">
-        <v>-1.931680867644571</v>
+        <v>-1.895442297176665</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" s="2" t="n">
-        <v>45561</v>
+        <v>45555</v>
       </c>
       <c r="B672" t="n">
-        <v>-1.972801741839866</v>
+        <v>-1.895181019217382</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" s="2" t="n">
-        <v>45562</v>
+        <v>45558</v>
       </c>
       <c r="B673" t="n">
-        <v>-1.94629775466901</v>
+        <v>-1.891914921959287</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" s="2" t="n">
-        <v>45565</v>
+        <v>45559</v>
       </c>
       <c r="B674" t="n">
-        <v>-1.958543431333776</v>
+        <v>-1.9292626406641</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" s="2" t="n">
-        <v>45567</v>
+        <v>45560</v>
       </c>
       <c r="B675" t="n">
-        <v>-2.051806711381076</v>
+        <v>-1.92984723286723</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" s="2" t="n">
-        <v>45568</v>
+        <v>45561</v>
       </c>
       <c r="B676" t="n">
-        <v>-2.057449101095947</v>
+        <v>-1.969796376314346</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" s="2" t="n">
-        <v>45569</v>
+        <v>45562</v>
       </c>
       <c r="B677" t="n">
-        <v>-2.06736813749914</v>
+        <v>-1.943422504657494</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" s="2" t="n">
-        <v>45572</v>
+        <v>45565</v>
       </c>
       <c r="B678" t="n">
-        <v>-2.058742702670937</v>
+        <v>-1.955632420164499</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" s="2" t="n">
-        <v>45573</v>
+        <v>45567</v>
       </c>
       <c r="B679" t="n">
-        <v>-2.436735346251702</v>
+        <v>-2.04839493138893</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" s="2" t="n">
-        <v>45574</v>
+        <v>45568</v>
       </c>
       <c r="B680" t="n">
-        <v>-2.443401110597744</v>
+        <v>-2.054004113533153</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" s="2" t="n">
-        <v>45575</v>
+        <v>45569</v>
       </c>
       <c r="B681" t="n">
-        <v>-2.486603803085944</v>
+        <v>-2.063888034998608</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" s="2" t="n">
-        <v>45579</v>
+        <v>45572</v>
       </c>
       <c r="B682" t="n">
-        <v>-2.432230560713692</v>
+        <v>-2.054013835109422</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" s="2" t="n">
-        <v>45580</v>
+        <v>45573</v>
       </c>
       <c r="B683" t="n">
-        <v>-2.511159726201465</v>
+        <v>-2.424699015123887</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" s="2" t="n">
-        <v>45581</v>
+        <v>45574</v>
       </c>
       <c r="B684" t="n">
-        <v>-2.484385353238745</v>
+        <v>-2.429053475444207</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" s="2" t="n">
-        <v>45582</v>
+        <v>45575</v>
       </c>
       <c r="B685" t="n">
-        <v>-2.493177035413247</v>
+        <v>-2.477485130711991</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" s="2" t="n">
-        <v>45583</v>
+        <v>45579</v>
       </c>
       <c r="B686" t="n">
-        <v>-2.583219464726293</v>
+        <v>-2.424094116204393</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" s="2" t="n">
-        <v>45586</v>
+        <v>45580</v>
       </c>
       <c r="B687" t="n">
-        <v>-2.599327535866369</v>
+        <v>-2.506403478325546</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" s="2" t="n">
-        <v>45587</v>
+        <v>45581</v>
       </c>
       <c r="B688" t="n">
-        <v>-2.599119891565617</v>
+        <v>-2.478935083624235</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" s="2" t="n">
-        <v>45588</v>
+        <v>45582</v>
       </c>
       <c r="B689" t="n">
-        <v>-2.612998806611083</v>
+        <v>-2.486904206369076</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" s="2" t="n">
-        <v>45589</v>
+        <v>45583</v>
       </c>
       <c r="B690" t="n">
-        <v>-2.592352588418176</v>
+        <v>-2.57871715176385</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" s="2" t="n">
-        <v>45590</v>
+        <v>45586</v>
       </c>
       <c r="B691" t="n">
-        <v>-2.594600598717096</v>
+        <v>-2.594695073591555</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" s="2" t="n">
-        <v>45593</v>
+        <v>45587</v>
       </c>
       <c r="B692" t="n">
-        <v>-2.59457649068767</v>
+        <v>-2.594569056637257</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" s="2" t="n">
-        <v>45594</v>
+        <v>45588</v>
       </c>
       <c r="B693" t="n">
-        <v>-2.546876801650944</v>
+        <v>-2.605694792502198</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" s="2" t="n">
-        <v>45595</v>
+        <v>45589</v>
       </c>
       <c r="B694" t="n">
-        <v>-2.736726827258681</v>
+        <v>-2.585015660677764</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" s="2" t="n">
-        <v>45596</v>
+        <v>45590</v>
       </c>
       <c r="B695" t="n">
-        <v>-2.734320224456941</v>
+        <v>-2.587228209801757</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" s="2" t="n">
-        <v>45597</v>
+        <v>45593</v>
       </c>
       <c r="B696" t="n">
-        <v>-2.737107794948388</v>
+        <v>-2.587210813716295</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" s="2" t="n">
-        <v>45600</v>
+        <v>45594</v>
       </c>
       <c r="B697" t="n">
-        <v>-2.728338720649532</v>
+        <v>-2.536139843446941</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" s="2" t="n">
-        <v>45601</v>
+        <v>45595</v>
       </c>
       <c r="B698" t="n">
-        <v>-2.783190662193943</v>
+        <v>-2.719822391730705</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" s="2" t="n">
-        <v>45602</v>
+        <v>45596</v>
       </c>
       <c r="B699" t="n">
-        <v>-2.840131534454844</v>
+        <v>-2.716817833873916</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" s="2" t="n">
-        <v>45603</v>
+        <v>45597</v>
       </c>
       <c r="B700" t="n">
-        <v>-2.862000045046721</v>
+        <v>-2.717966498965279</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" s="2" t="n">
-        <v>45604</v>
+        <v>45600</v>
       </c>
       <c r="B701" t="n">
-        <v>-2.779342478966189</v>
+        <v>-2.71322648221045</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" s="2" t="n">
-        <v>45607</v>
+        <v>45601</v>
       </c>
       <c r="B702" t="n">
-        <v>-2.802255771905597</v>
+        <v>-2.766333692444388</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" s="2" t="n">
-        <v>45608</v>
+        <v>45602</v>
       </c>
       <c r="B703" t="n">
-        <v>-2.922523606128649</v>
+        <v>-2.828610741223438</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" s="2" t="n">
-        <v>45609</v>
+        <v>45603</v>
       </c>
       <c r="B704" t="n">
-        <v>-2.903238007966181</v>
+        <v>-2.855952189470592</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" s="2" t="n">
-        <v>45610</v>
+        <v>45604</v>
       </c>
       <c r="B705" t="n">
-        <v>-2.887082467515181</v>
+        <v>-2.785248829972958</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" s="2" t="n">
-        <v>45611</v>
+        <v>45607</v>
       </c>
       <c r="B706" t="n">
-        <v>-2.878123934115205</v>
+        <v>-2.804345617443309</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" s="2" t="n">
-        <v>45614</v>
+        <v>45608</v>
       </c>
       <c r="B707" t="n">
-        <v>-2.887721217138706</v>
+        <v>-2.925048316235225</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" s="2" t="n">
-        <v>45615</v>
+        <v>45609</v>
       </c>
       <c r="B708" t="n">
-        <v>-2.883543605660134</v>
+        <v>-2.905685556466963</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" s="2" t="n">
-        <v>45616</v>
+        <v>45610</v>
       </c>
       <c r="B709" t="n">
-        <v>-2.879079246759768</v>
+        <v>-2.885573518148129</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" s="2" t="n">
-        <v>45617</v>
+        <v>45611</v>
       </c>
       <c r="B710" t="n">
-        <v>-2.88220969877004</v>
+        <v>-2.876632887778118</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" s="2" t="n">
-        <v>45618</v>
+        <v>45614</v>
       </c>
       <c r="B711" t="n">
-        <v>-2.941247878625459</v>
+        <v>-2.886849854451421</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" s="2" t="n">
-        <v>45621</v>
+        <v>45615</v>
       </c>
       <c r="B712" t="n">
-        <v>-2.913407375758209</v>
+        <v>-2.881610737165088</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" s="2" t="n">
-        <v>45622</v>
+        <v>45616</v>
       </c>
       <c r="B713" t="n">
-        <v>-2.911967253287934</v>
+        <v>-2.876262485325568</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" s="2" t="n">
-        <v>45623</v>
+        <v>45617</v>
       </c>
       <c r="B714" t="n">
-        <v>-3.019345642346509</v>
+        <v>-2.879947758582029</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" s="2" t="n">
-        <v>45624</v>
+        <v>45618</v>
       </c>
       <c r="B715" t="n">
-        <v>-3.051071987424678</v>
+        <v>-2.936347907353442</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" s="2" t="n">
-        <v>45625</v>
+        <v>45621</v>
       </c>
       <c r="B716" t="n">
-        <v>-2.944754866961822</v>
+        <v>-2.904324906176347</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" s="2" t="n">
-        <v>45628</v>
+        <v>45622</v>
       </c>
       <c r="B717" t="n">
-        <v>-2.938304991356049</v>
+        <v>-2.901912605839922</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" s="2" t="n">
-        <v>45629</v>
+        <v>45623</v>
       </c>
       <c r="B718" t="n">
-        <v>-2.951598205963623</v>
+        <v>-3.018357672320832</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" s="2" t="n">
-        <v>45630</v>
+        <v>45624</v>
       </c>
       <c r="B719" t="n">
-        <v>-2.923173028994533</v>
+        <v>-3.052963825538098</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" s="2" t="n">
-        <v>45631</v>
+        <v>45625</v>
       </c>
       <c r="B720" t="n">
-        <v>-2.92127073328201</v>
+        <v>-2.942948547510639</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" s="2" t="n">
-        <v>45632</v>
+        <v>45628</v>
       </c>
       <c r="B721" t="n">
-        <v>-2.967642756766899</v>
+        <v>-2.940391017067511</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" s="2" t="n">
-        <v>45635</v>
+        <v>45629</v>
       </c>
       <c r="B722" t="n">
-        <v>-3.106019581624743</v>
+        <v>-2.947761424616881</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" s="2" t="n">
-        <v>45636</v>
+        <v>45630</v>
       </c>
       <c r="B723" t="n">
-        <v>-3.090231204021975</v>
+        <v>-2.919476267748753</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" s="2" t="n">
-        <v>45637</v>
+        <v>45631</v>
       </c>
       <c r="B724" t="n">
-        <v>-3.033192029272138</v>
+        <v>-2.919187745078924</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" s="2" t="n">
-        <v>45638</v>
+        <v>45632</v>
       </c>
       <c r="B725" t="n">
-        <v>-3.057364521563134</v>
+        <v>-2.964960828198995</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" s="2" t="n">
-        <v>45639</v>
+        <v>45635</v>
       </c>
       <c r="B726" t="n">
-        <v>-3.128628872981838</v>
+        <v>-3.089904365729335</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" s="2" t="n">
-        <v>45642</v>
+        <v>45636</v>
       </c>
       <c r="B727" t="n">
-        <v>-3.141784223519996</v>
+        <v>-3.072611029091962</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" s="2" t="n">
-        <v>45643</v>
+        <v>45637</v>
       </c>
       <c r="B728" t="n">
-        <v>-3.071004804016854</v>
+        <v>-3.01359426573144</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" s="2" t="n">
-        <v>45644</v>
+        <v>45638</v>
       </c>
       <c r="B729" t="n">
-        <v>-3.062519828533385</v>
+        <v>-3.037308050336591</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" s="2" t="n">
-        <v>45645</v>
+        <v>45639</v>
       </c>
       <c r="B730" t="n">
-        <v>-3.010878387455562</v>
+        <v>-3.113089562181739</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" s="2" t="n">
-        <v>45646</v>
+        <v>45642</v>
       </c>
       <c r="B731" t="n">
-        <v>-3.008552729161099</v>
+        <v>-3.126450364959859</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" s="2" t="n">
-        <v>45649</v>
+        <v>45643</v>
       </c>
       <c r="B732" t="n">
-        <v>-2.962046695412371</v>
+        <v>-3.060539521593454</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" s="2" t="n">
-        <v>45650</v>
+        <v>45644</v>
       </c>
       <c r="B733" t="n">
-        <v>-2.981956181824107</v>
+        <v>-3.049575070791575</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" s="2" t="n">
-        <v>45653</v>
+        <v>45645</v>
       </c>
       <c r="B734" t="n">
-        <v>-2.982917692185094</v>
+        <v>-2.993621790760549</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" s="2" t="n">
-        <v>45656</v>
+        <v>45646</v>
       </c>
       <c r="B735" t="n">
-        <v>-2.984453297407048</v>
+        <v>-2.991622564215628</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" s="2" t="n">
-        <v>45657</v>
+        <v>45649</v>
       </c>
       <c r="B736" t="n">
-        <v>-2.853137316800404</v>
+        <v>-2.939133498117617</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" s="2" t="n">
-        <v>45659</v>
+        <v>45650</v>
       </c>
       <c r="B737" t="n">
-        <v>-2.927584727345915</v>
+        <v>-2.965815800428941</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" s="2" t="n">
-        <v>45660</v>
+        <v>45653</v>
       </c>
       <c r="B738" t="n">
-        <v>-2.909521497118032</v>
+        <v>-2.968035151385531</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" s="2" t="n">
-        <v>45663</v>
+        <v>45656</v>
       </c>
       <c r="B739" t="n">
-        <v>-2.886324560569764</v>
+        <v>-2.968777678888308</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" s="2" t="n">
-        <v>45664</v>
+        <v>45657</v>
       </c>
       <c r="B740" t="n">
-        <v>-2.862591821462483</v>
+        <v>-2.848895142963292</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" s="2" t="n">
-        <v>45665</v>
+        <v>45659</v>
       </c>
       <c r="B741" t="n">
-        <v>-2.859722908074465</v>
+        <v>-2.926715205662575</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" s="2" t="n">
-        <v>45666</v>
+        <v>45660</v>
       </c>
       <c r="B742" t="n">
-        <v>-2.774168971481267</v>
+        <v>-2.902875277838599</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" s="2" t="n">
-        <v>45667</v>
+        <v>45663</v>
       </c>
       <c r="B743" t="n">
-        <v>-2.78259567273032</v>
+        <v>-2.8835155111122</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" s="2" t="n">
-        <v>45670</v>
+        <v>45664</v>
       </c>
       <c r="B744" t="n">
-        <v>-2.647619516006419</v>
+        <v>-2.85989325588469</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" s="2" t="n">
-        <v>45671</v>
+        <v>45665</v>
       </c>
       <c r="B745" t="n">
-        <v>-2.679614382622422</v>
+        <v>-2.857066918041852</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" s="2" t="n">
-        <v>45672</v>
+        <v>45666</v>
       </c>
       <c r="B746" t="n">
-        <v>-2.654920194403312</v>
+        <v>-2.772238350650255</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" s="2" t="n">
-        <v>45673</v>
+        <v>45667</v>
       </c>
       <c r="B747" t="n">
-        <v>-2.672714775554031</v>
+        <v>-2.780096548740311</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" s="2" t="n">
-        <v>45674</v>
+        <v>45670</v>
       </c>
       <c r="B748" t="n">
-        <v>-2.645429162957638</v>
+        <v>-2.639341295949498</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" s="2" t="n">
-        <v>45677</v>
+        <v>45671</v>
       </c>
       <c r="B749" t="n">
-        <v>-2.532323116334586</v>
+        <v>-2.672802826007232</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" s="2" t="n">
-        <v>45678</v>
+        <v>45672</v>
       </c>
       <c r="B750" t="n">
-        <v>-2.536573050429746</v>
+        <v>-2.648175908384248</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" s="2" t="n">
-        <v>45679</v>
+        <v>45673</v>
       </c>
       <c r="B751" t="n">
-        <v>-2.543122499395423</v>
+        <v>-2.667144342955079</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" s="2" t="n">
-        <v>45680</v>
+        <v>45674</v>
       </c>
       <c r="B752" t="n">
-        <v>-2.473901241653464</v>
+        <v>-2.639903151459036</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" s="2" t="n">
-        <v>45681</v>
+        <v>45677</v>
       </c>
       <c r="B753" t="n">
-        <v>-2.494309776070513</v>
+        <v>-2.526497882164145</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" s="2" t="n">
-        <v>45684</v>
+        <v>45678</v>
       </c>
       <c r="B754" t="n">
-        <v>-2.427150916501883</v>
+        <v>-2.531426186890936</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" s="2" t="n">
-        <v>45685</v>
+        <v>45679</v>
       </c>
       <c r="B755" t="n">
-        <v>-2.426967809435937</v>
+        <v>-2.542400109466756</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" s="2" t="n">
-        <v>45691</v>
+        <v>45680</v>
       </c>
       <c r="B756" t="n">
-        <v>-2.426266583140209</v>
+        <v>-2.473217592636158</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" s="2" t="n">
-        <v>45692</v>
+        <v>45681</v>
       </c>
       <c r="B757" t="n">
-        <v>-2.425847245697954</v>
+        <v>-2.496302287819907</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" s="2" t="n">
-        <v>45693</v>
+        <v>45684</v>
       </c>
       <c r="B758" t="n">
-        <v>-2.362534261836374</v>
+        <v>-2.424402268992513</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" s="2" t="n">
-        <v>45694</v>
+        <v>45685</v>
       </c>
       <c r="B759" t="n">
-        <v>-2.371336040427294</v>
+        <v>-2.424220037129361</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" s="2" t="n">
-        <v>45695</v>
+        <v>45691</v>
       </c>
       <c r="B760" t="n">
-        <v>-2.36288156160346</v>
+        <v>-2.423461031366069</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" s="2" t="n">
-        <v>45698</v>
+        <v>45692</v>
       </c>
       <c r="B761" t="n">
-        <v>-2.380743760699624</v>
+        <v>-2.419633251066194</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" s="2" t="n">
-        <v>45699</v>
+        <v>45693</v>
       </c>
       <c r="B762" t="n">
-        <v>-2.384826165932126</v>
+        <v>-2.357007364625136</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" s="2" t="n">
-        <v>45700</v>
+        <v>45694</v>
       </c>
       <c r="B763" t="n">
-        <v>-2.419223718929989</v>
+        <v>-2.36762808329366</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" s="2" t="n">
-        <v>45701</v>
+        <v>45695</v>
       </c>
       <c r="B764" t="n">
-        <v>-2.394802798377601</v>
+        <v>-2.356368799706638</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" s="2" t="n">
-        <v>45702</v>
+        <v>45698</v>
       </c>
       <c r="B765" t="n">
-        <v>-2.473228016286746</v>
+        <v>-2.373862946834761</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" s="2" t="n">
-        <v>45705</v>
+        <v>45699</v>
       </c>
       <c r="B766" t="n">
-        <v>-2.436038022537629</v>
+        <v>-2.378458337603789</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" s="2" t="n">
-        <v>45706</v>
+        <v>45700</v>
       </c>
       <c r="B767" t="n">
-        <v>-2.451896183320848</v>
+        <v>-2.410247408201174</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" s="2" t="n">
-        <v>45707</v>
+        <v>45701</v>
       </c>
       <c r="B768" t="n">
-        <v>-2.421155300481703</v>
+        <v>-2.384487534090901</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" s="2" t="n">
-        <v>45708</v>
+        <v>45702</v>
       </c>
       <c r="B769" t="n">
-        <v>-2.407356164773326</v>
+        <v>-2.46563730349035</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" s="2" t="n">
-        <v>45709</v>
+        <v>45705</v>
       </c>
       <c r="B770" t="n">
-        <v>-2.509624860193736</v>
+        <v>-2.42896674401757</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" s="2" t="n">
-        <v>45712</v>
+        <v>45706</v>
       </c>
       <c r="B771" t="n">
-        <v>-2.474356680140219</v>
+        <v>-2.44482442246231</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" s="2" t="n">
-        <v>45713</v>
+        <v>45707</v>
       </c>
       <c r="B772" t="n">
-        <v>-2.485858037921326</v>
+        <v>-2.414478723083986</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" s="2" t="n">
-        <v>45714</v>
+        <v>45708</v>
       </c>
       <c r="B773" t="n">
-        <v>-2.556966419044631</v>
+        <v>-2.40084987036876</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" s="2" t="n">
-        <v>45715</v>
+        <v>45709</v>
       </c>
       <c r="B774" t="n">
-        <v>-2.553449149864842</v>
+        <v>-2.50175004247675</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" s="2" t="n">
-        <v>45716</v>
+        <v>45712</v>
       </c>
       <c r="B775" t="n">
-        <v>-2.635860281832941</v>
+        <v>-2.467636187328654</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" s="2" t="n">
-        <v>45719</v>
+        <v>45713</v>
       </c>
       <c r="B776" t="n">
-        <v>-2.635875722854969</v>
+        <v>-2.477393201284582</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" s="2" t="n">
-        <v>45720</v>
+        <v>45714</v>
       </c>
       <c r="B777" t="n">
-        <v>-2.637035957130486</v>
+        <v>-2.54676794896352</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" s="2" t="n">
-        <v>45721</v>
+        <v>45715</v>
       </c>
       <c r="B778" t="n">
-        <v>-2.691064005689478</v>
+        <v>-2.543155259426435</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" s="2" t="n">
-        <v>45722</v>
+        <v>45716</v>
       </c>
       <c r="B779" t="n">
-        <v>-1.861557969404137</v>
+        <v>-2.629062237704014</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" s="2" t="n">
-        <v>45723</v>
+        <v>45719</v>
       </c>
       <c r="B780" t="n">
-        <v>-1.857188982315105</v>
+        <v>-2.629426637835445</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" s="2" t="n">
-        <v>45726</v>
+        <v>45720</v>
       </c>
       <c r="B781" t="n">
-        <v>-1.86156372352157</v>
+        <v>-2.630503252017005</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" s="2" t="n">
-        <v>45727</v>
+        <v>45721</v>
       </c>
       <c r="B782" t="n">
-        <v>-1.851506626224837</v>
+        <v>-2.683887843533471</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" s="2" t="n">
-        <v>45728</v>
+        <v>45722</v>
       </c>
       <c r="B783" t="n">
-        <v>-1.849993346825837</v>
+        <v>-1.860601110810364</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" s="2" t="n">
-        <v>45729</v>
+        <v>45723</v>
       </c>
       <c r="B784" t="n">
-        <v>-1.840138884618058</v>
+        <v>-1.856979444985754</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" s="2" t="n">
-        <v>45730</v>
+        <v>45726</v>
       </c>
       <c r="B785" t="n">
-        <v>-1.847974328218034</v>
+        <v>-1.861344460529889</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" s="2" t="n">
-        <v>45733</v>
+        <v>45727</v>
       </c>
       <c r="B786" t="n">
-        <v>-1.841728201037655</v>
+        <v>-1.851353863891318</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" s="2" t="n">
-        <v>45734</v>
+        <v>45728</v>
       </c>
       <c r="B787" t="n">
-        <v>-1.846493462504822</v>
+        <v>-1.84928231462997</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" s="2" t="n">
-        <v>45735</v>
+        <v>45729</v>
       </c>
       <c r="B788" t="n">
-        <v>-1.845528712275713</v>
+        <v>-1.840128625717867</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" s="2" t="n">
-        <v>45736</v>
+        <v>45730</v>
       </c>
       <c r="B789" t="n">
-        <v>-1.844794224314936</v>
+        <v>-1.848734626647614</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" s="2" t="n">
-        <v>45737</v>
+        <v>45733</v>
       </c>
       <c r="B790" t="n">
-        <v>-1.853745124676065</v>
+        <v>-1.842470931600574</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" s="2" t="n">
-        <v>45740</v>
+        <v>45734</v>
       </c>
       <c r="B791" t="n">
-        <v>-1.854737750539785</v>
+        <v>-1.847228562018274</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" s="2" t="n">
-        <v>45741</v>
+        <v>45735</v>
       </c>
       <c r="B792" t="n">
-        <v>-1.865235640130219</v>
+        <v>-1.845911631402451</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" s="2" t="n">
-        <v>45742</v>
+        <v>45736</v>
       </c>
       <c r="B793" t="n">
-        <v>-1.86408249548281</v>
+        <v>-1.845193450365666</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" s="2" t="n">
-        <v>45743</v>
+        <v>45737</v>
       </c>
       <c r="B794" t="n">
-        <v>-1.863368202486255</v>
+        <v>-1.853881351467379</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" s="2" t="n">
-        <v>45744</v>
+        <v>45740</v>
       </c>
       <c r="B795" t="n">
-        <v>-1.858391704549477</v>
+        <v>-1.854875044997332</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" s="2" t="n">
-        <v>45747</v>
+        <v>45741</v>
       </c>
       <c r="B796" t="n">
-        <v>-1.859745084233517</v>
+        <v>-1.865384719832385</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" s="2" t="n">
-        <v>45748</v>
+        <v>45742</v>
       </c>
       <c r="B797" t="n">
-        <v>-1.859863943767558</v>
+        <v>-1.864551794959937</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" s="2" t="n">
-        <v>45749</v>
+        <v>45743</v>
       </c>
       <c r="B798" t="n">
-        <v>-1.859470767812567</v>
+        <v>-1.864310147913535</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" s="2" t="n">
-        <v>45750</v>
+        <v>45744</v>
       </c>
       <c r="B799" t="n">
-        <v>-1.864654695868409</v>
+        <v>-1.858681447650744</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" s="2" t="n">
-        <v>45754</v>
+        <v>45747</v>
       </c>
       <c r="B800" t="n">
-        <v>-2.739544350623103</v>
+        <v>-1.859894475670752</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" s="2" t="n">
-        <v>45755</v>
+        <v>45748</v>
       </c>
       <c r="B801" t="n">
-        <v>-2.722199056581672</v>
+        <v>-1.859954344922172</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" s="2" t="n">
-        <v>45756</v>
+        <v>45749</v>
       </c>
       <c r="B802" t="n">
-        <v>-2.673725996306882</v>
+        <v>-1.859575672865472</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" s="2" t="n">
-        <v>45757</v>
+        <v>45750</v>
       </c>
       <c r="B803" t="n">
-        <v>-2.722862617184393</v>
+        <v>-1.864508089346665</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" s="2" t="n">
-        <v>45758</v>
+        <v>45754</v>
       </c>
       <c r="B804" t="n">
-        <v>-2.7342591903035</v>
+        <v>-2.739527417820419</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" s="2" t="n">
-        <v>45761</v>
+        <v>45755</v>
       </c>
       <c r="B805" t="n">
-        <v>-2.803060691478213</v>
+        <v>-2.71330515042595</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" s="2" t="n">
-        <v>45762</v>
+        <v>45756</v>
       </c>
       <c r="B806" t="n">
-        <v>-2.776843908903787</v>
+        <v>-2.664594518432544</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" s="2" t="n">
-        <v>45763</v>
+        <v>45757</v>
       </c>
       <c r="B807" t="n">
-        <v>-2.820407053964426</v>
+        <v>-2.712748275879985</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" s="2" t="n">
-        <v>45764</v>
+        <v>45758</v>
       </c>
       <c r="B808" t="n">
-        <v>-2.842573190699106</v>
+        <v>-2.723152710811678</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" s="2" t="n">
-        <v>45769</v>
+        <v>45761</v>
       </c>
       <c r="B809" t="n">
-        <v>-2.849610501459149</v>
+        <v>-2.79026932892288</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" s="2" t="n">
-        <v>45770</v>
+        <v>45762</v>
       </c>
       <c r="B810" t="n">
-        <v>-2.901036120714999</v>
+        <v>-2.7641433846256</v>
       </c>
     </row>
     <row r="811">
       <c r="A811" s="2" t="n">
-        <v>45771</v>
+        <v>45763</v>
       </c>
       <c r="B811" t="n">
-        <v>-2.903721374244258</v>
+        <v>-2.806608034193057</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" s="2" t="n">
-        <v>45772</v>
+        <v>45764</v>
       </c>
       <c r="B812" t="n">
-        <v>-2.904085972340412</v>
+        <v>-2.828180143507388</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" s="2" t="n">
-        <v>45775</v>
+        <v>45769</v>
       </c>
       <c r="B813" t="n">
-        <v>-2.874639988021692</v>
+        <v>-2.837093121862559</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" s="2" t="n">
-        <v>45776</v>
+        <v>45770</v>
       </c>
       <c r="B814" t="n">
-        <v>-2.865573004363495</v>
+        <v>-2.890682323380113</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" s="2" t="n">
-        <v>45777</v>
+        <v>45771</v>
       </c>
       <c r="B815" t="n">
-        <v>-2.86714831347934</v>
+        <v>-2.895548579934247</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" s="2" t="n">
-        <v>45779</v>
+        <v>45772</v>
       </c>
       <c r="B816" t="n">
-        <v>-2.875554098210891</v>
+        <v>-2.895912719807498</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" s="2" t="n">
-        <v>45783</v>
+        <v>45775</v>
       </c>
       <c r="B817" t="n">
-        <v>-2.877288441013717</v>
+        <v>-2.870352139230247</v>
       </c>
     </row>
     <row r="818">
       <c r="A818" s="2" t="n">
-        <v>45784</v>
+        <v>45776</v>
       </c>
       <c r="B818" t="n">
-        <v>-2.861981988872726</v>
+        <v>-2.858998477288185</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" s="2" t="n">
-        <v>45785</v>
+        <v>45777</v>
       </c>
       <c r="B819" t="n">
-        <v>-2.864488431393323</v>
+        <v>-2.860698858400661</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" s="2" t="n">
-        <v>45786</v>
+        <v>45779</v>
       </c>
       <c r="B820" t="n">
-        <v>-2.837566085502236</v>
+        <v>-2.877860697021936</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" s="2" t="n">
-        <v>45789</v>
+        <v>45783</v>
       </c>
       <c r="B821" t="n">
-        <v>-2.983975649303766</v>
+        <v>-2.882345697413267</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" s="2" t="n">
-        <v>45790</v>
+        <v>45784</v>
       </c>
       <c r="B822" t="n">
-        <v>-3.047048745771361</v>
+        <v>-2.866754777852461</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" s="2" t="n">
-        <v>45791</v>
+        <v>45785</v>
       </c>
       <c r="B823" t="n">
-        <v>-3.143715439479803</v>
+        <v>-2.869287558260261</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" s="2" t="n">
-        <v>45792</v>
+        <v>45786</v>
       </c>
       <c r="B824" t="n">
-        <v>-3.141264305880243</v>
+        <v>-2.843842705420895</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" s="2" t="n">
-        <v>45793</v>
+        <v>45789</v>
       </c>
       <c r="B825" t="n">
-        <v>-3.122889933066825</v>
+        <v>-2.987238457095193</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" s="2" t="n">
-        <v>45796</v>
+        <v>45790</v>
       </c>
       <c r="B826" t="n">
-        <v>-3.118774834787501</v>
+        <v>-3.054982426723158</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" s="2" t="n">
-        <v>45797</v>
+        <v>45791</v>
       </c>
       <c r="B827" t="n">
-        <v>-3.142506484560517</v>
+        <v>-3.16439250503646</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" s="2" t="n">
-        <v>45798</v>
+        <v>45792</v>
       </c>
       <c r="B828" t="n">
-        <v>-3.05706302346735</v>
+        <v>-3.158269353515733</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" s="2" t="n">
-        <v>45799</v>
+        <v>45793</v>
       </c>
       <c r="B829" t="n">
-        <v>-3.069738050430806</v>
+        <v>-3.140977490886132</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" s="2" t="n">
-        <v>45800</v>
+        <v>45796</v>
       </c>
       <c r="B830" t="n">
-        <v>-3.05204204153604</v>
+        <v>-3.138312200355693</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" s="2" t="n">
-        <v>45803</v>
+        <v>45797</v>
       </c>
       <c r="B831" t="n">
-        <v>-3.00796874498949</v>
+        <v>-3.157958856967646</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" s="2" t="n">
-        <v>45804</v>
+        <v>45798</v>
       </c>
       <c r="B832" t="n">
-        <v>-2.981636730901679</v>
+        <v>-3.069988681460053</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" s="2" t="n">
-        <v>45805</v>
+        <v>45799</v>
       </c>
       <c r="B833" t="n">
-        <v>-2.978958537696218</v>
+        <v>-3.074367065149437</v>
       </c>
     </row>
     <row r="834">
       <c r="A834" s="2" t="n">
-        <v>45806</v>
+        <v>45800</v>
       </c>
       <c r="B834" t="n">
-        <v>-3.014268810635657</v>
+        <v>-3.062834760619229</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" s="2" t="n">
-        <v>45807</v>
+        <v>45803</v>
       </c>
       <c r="B835" t="n">
-        <v>-3.032396672583737</v>
+        <v>-3.006434910653273</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" s="2" t="n">
-        <v>45810</v>
+        <v>45804</v>
       </c>
       <c r="B836" t="n">
-        <v>-3.034902953403886</v>
+        <v>-2.984115909092522</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" s="2" t="n">
-        <v>45811</v>
+        <v>45805</v>
       </c>
       <c r="B837" t="n">
-        <v>-3.082117598930043</v>
+        <v>-2.981416509916776</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" s="2" t="n">
-        <v>45812</v>
+        <v>45806</v>
       </c>
       <c r="B838" t="n">
-        <v>-3.085001076803115</v>
+        <v>-3.012324564171664</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" s="2" t="n">
-        <v>45813</v>
+        <v>45807</v>
       </c>
       <c r="B839" t="n">
-        <v>-3.109145279587038</v>
+        <v>-3.030396643402439</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" s="2" t="n">
-        <v>45814</v>
+        <v>45810</v>
       </c>
       <c r="B840" t="n">
-        <v>-3.082305482964315</v>
+        <v>-3.029160783157731</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" s="2" t="n">
-        <v>45817</v>
+        <v>45811</v>
       </c>
       <c r="B841" t="n">
-        <v>-3.102322700783013</v>
+        <v>-3.071568404957543</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" s="2" t="n">
-        <v>45818</v>
+        <v>45812</v>
       </c>
       <c r="B842" t="n">
-        <v>-3.094265845527816</v>
+        <v>-3.071942979331094</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" s="2" t="n">
-        <v>45819</v>
+        <v>45813</v>
       </c>
       <c r="B843" t="n">
-        <v>-3.108094093363671</v>
+        <v>-3.094977380163744</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" s="2" t="n">
-        <v>45820</v>
+        <v>45814</v>
       </c>
       <c r="B844" t="n">
-        <v>-3.140079821397731</v>
+        <v>-3.064720502061059</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" s="2" t="n">
-        <v>45821</v>
+        <v>45817</v>
       </c>
       <c r="B845" t="n">
-        <v>-3.094522700734875</v>
+        <v>-3.084092631070814</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" s="2" t="n">
-        <v>45824</v>
+        <v>45818</v>
       </c>
       <c r="B846" t="n">
-        <v>-3.112185287411674</v>
+        <v>-3.076328315441455</v>
       </c>
     </row>
     <row r="847">
       <c r="A847" s="2" t="n">
-        <v>45825</v>
+        <v>45819</v>
       </c>
       <c r="B847" t="n">
-        <v>-3.116429729778336</v>
+        <v>-3.095114345298002</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" s="2" t="n">
-        <v>45826</v>
+        <v>45820</v>
       </c>
       <c r="B848" t="n">
-        <v>-3.104595648614266</v>
+        <v>-3.125032916816493</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" s="2" t="n">
-        <v>45827</v>
+        <v>45821</v>
       </c>
       <c r="B849" t="n">
-        <v>-3.204443811164394</v>
+        <v>-3.083858693847645</v>
       </c>
     </row>
     <row r="850">
       <c r="A850" s="2" t="n">
-        <v>45828</v>
+        <v>45824</v>
       </c>
       <c r="B850" t="n">
-        <v>-3.226763602558277</v>
+        <v>-3.099741552100162</v>
       </c>
     </row>
     <row r="851">
       <c r="A851" s="2" t="n">
-        <v>45831</v>
+        <v>45825</v>
       </c>
       <c r="B851" t="n">
-        <v>-3.179492829740567</v>
+        <v>-3.102228456942833</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" s="2" t="n">
-        <v>45832</v>
+        <v>45826</v>
       </c>
       <c r="B852" t="n">
-        <v>-3.295987268185697</v>
+        <v>-3.095211294341858</v>
       </c>
     </row>
     <row r="853">
       <c r="A853" s="2" t="n">
-        <v>45833</v>
+        <v>45827</v>
       </c>
       <c r="B853" t="n">
-        <v>-3.321157004356297</v>
+        <v>-3.195879291285112</v>
       </c>
     </row>
     <row r="854">
       <c r="A854" s="2" t="n">
-        <v>45834</v>
+        <v>45828</v>
       </c>
       <c r="B854" t="n">
-        <v>-3.314969353441092</v>
+        <v>-3.229380840188813</v>
       </c>
     </row>
     <row r="855">
       <c r="A855" s="2" t="n">
-        <v>45835</v>
+        <v>45831</v>
       </c>
       <c r="B855" t="n">
-        <v>-3.316305709684546</v>
+        <v>-3.166880132227411</v>
       </c>
     </row>
     <row r="856">
       <c r="A856" s="2" t="n">
-        <v>45838</v>
+        <v>45832</v>
       </c>
       <c r="B856" t="n">
-        <v>-3.265612163343048</v>
+        <v>-3.291941738269555</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" s="2" t="n">
-        <v>45840</v>
+        <v>45833</v>
       </c>
       <c r="B857" t="n">
-        <v>-3.194464325165153</v>
+        <v>-3.303328171218516</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" s="2" t="n">
-        <v>45841</v>
+        <v>45834</v>
       </c>
       <c r="B858" t="n">
-        <v>-3.16546185396414</v>
+        <v>-3.297351818829317</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" s="2" t="n">
-        <v>45842</v>
+        <v>45835</v>
       </c>
       <c r="B859" t="n">
-        <v>-3.153237397865345</v>
+        <v>-3.298642928650533</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" s="2" t="n">
-        <v>45845</v>
+        <v>45838</v>
       </c>
       <c r="B860" t="n">
-        <v>-3.142567108116542</v>
+        <v>-3.249589990224478</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" s="2" t="n">
-        <v>45846</v>
+        <v>45840</v>
       </c>
       <c r="B861" t="n">
-        <v>-3.17302315476164</v>
+        <v>-3.180487474779566</v>
       </c>
     </row>
     <row r="862">
       <c r="A862" s="2" t="n">
-        <v>45847</v>
+        <v>45841</v>
       </c>
       <c r="B862" t="n">
-        <v>-3.197096265005858</v>
+        <v>-3.150249031740306</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" s="2" t="n">
-        <v>45848</v>
+        <v>45842</v>
       </c>
       <c r="B863" t="n">
-        <v>-3.19029146214646</v>
+        <v>-3.138363183759602</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" s="2" t="n">
-        <v>45849</v>
+        <v>45845</v>
       </c>
       <c r="B864" t="n">
-        <v>-3.196221534872012</v>
+        <v>-3.128520497704412</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" s="2" t="n">
-        <v>45852</v>
+        <v>45846</v>
       </c>
       <c r="B865" t="n">
-        <v>-3.196328301229082</v>
+        <v>-3.162245277562082</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" s="2" t="n">
-        <v>45853</v>
+        <v>45847</v>
       </c>
       <c r="B866" t="n">
-        <v>-3.102585880062666</v>
+        <v>-3.185772796837644</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" s="2" t="n">
-        <v>45854</v>
+        <v>45848</v>
       </c>
       <c r="B867" t="n">
-        <v>-3.103804457332562</v>
+        <v>-3.180779452885467</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" s="2" t="n">
-        <v>45855</v>
+        <v>45849</v>
       </c>
       <c r="B868" t="n">
-        <v>-3.086232222095735</v>
+        <v>-3.185418016167449</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" s="2" t="n">
-        <v>45856</v>
+        <v>45852</v>
       </c>
       <c r="B869" t="n">
-        <v>-3.121012706390245</v>
+        <v>-3.185603780800477</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" s="2" t="n">
-        <v>45859</v>
+        <v>45853</v>
       </c>
       <c r="B870" t="n">
-        <v>-3.130327574964832</v>
+        <v>-3.10264618835305</v>
       </c>
     </row>
     <row r="871">
       <c r="A871" s="2" t="n">
-        <v>45860</v>
+        <v>45854</v>
       </c>
       <c r="B871" t="n">
-        <v>-3.138215675828925</v>
+        <v>-3.105292647957799</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" s="2" t="n">
-        <v>45861</v>
+        <v>45855</v>
       </c>
       <c r="B872" t="n">
-        <v>-3.205816557414628</v>
+        <v>-3.087809557427186</v>
       </c>
     </row>
     <row r="873">
       <c r="A873" s="2" t="n">
-        <v>45862</v>
+        <v>45856</v>
       </c>
       <c r="B873" t="n">
-        <v>-3.188407783637132</v>
+        <v>-3.120641153402427</v>
       </c>
     </row>
     <row r="874">
       <c r="A874" s="2" t="n">
-        <v>45863</v>
+        <v>45859</v>
       </c>
       <c r="B874" t="n">
-        <v>-3.115445461723571</v>
+        <v>-3.127874848657389</v>
       </c>
     </row>
     <row r="875">
       <c r="A875" s="2" t="n">
-        <v>45866</v>
+        <v>45860</v>
       </c>
       <c r="B875" t="n">
-        <v>-3.09034785041259</v>
+        <v>-3.135126833633075</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" s="2" t="n">
-        <v>45867</v>
+        <v>45861</v>
       </c>
       <c r="B876" t="n">
-        <v>-3.055205221247419</v>
+        <v>-3.209781547978085</v>
       </c>
     </row>
     <row r="877">
       <c r="A877" s="2" t="n">
-        <v>45868</v>
+        <v>45862</v>
       </c>
       <c r="B877" t="n">
-        <v>-3.086091918037439</v>
+        <v>-3.19636450519443</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" s="2" t="n">
-        <v>45869</v>
+        <v>45863</v>
       </c>
       <c r="B878" t="n">
-        <v>-3.143038876221037</v>
+        <v>-3.118721132544117</v>
       </c>
     </row>
     <row r="879">
       <c r="A879" s="2" t="n">
-        <v>45870</v>
+        <v>45866</v>
       </c>
       <c r="B879" t="n">
-        <v>-3.073163069077924</v>
+        <v>-3.08881335644425</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" s="2" t="n">
-        <v>45873</v>
+        <v>45867</v>
       </c>
       <c r="B880" t="n">
-        <v>-3.086333937455182</v>
+        <v>-3.053748548905097</v>
       </c>
     </row>
     <row r="881">
       <c r="A881" s="2" t="n">
-        <v>45874</v>
+        <v>45868</v>
       </c>
       <c r="B881" t="n">
-        <v>-3.090831136617682</v>
+        <v>-3.084567052636955</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" s="2" t="n">
-        <v>45875</v>
+        <v>45869</v>
       </c>
       <c r="B882" t="n">
-        <v>-3.063627191080415</v>
+        <v>-3.141377626902632</v>
       </c>
     </row>
     <row r="883">
       <c r="A883" s="2" t="n">
-        <v>45876</v>
+        <v>45870</v>
       </c>
       <c r="B883" t="n">
-        <v>-3.02732342498927</v>
+        <v>-3.0644297415767</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" s="2" t="n">
-        <v>45877</v>
+        <v>45873</v>
       </c>
       <c r="B884" t="n">
-        <v>-3.026673944550044</v>
+        <v>-3.077387819672588</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" s="2" t="n">
-        <v>45880</v>
+        <v>45874</v>
       </c>
       <c r="B885" t="n">
-        <v>-2.99324381532237</v>
+        <v>-3.079984058152179</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" s="2" t="n">
-        <v>45881</v>
+        <v>45875</v>
       </c>
       <c r="B886" t="n">
-        <v>-2.972837480211057</v>
+        <v>-3.054024804558436</v>
       </c>
     </row>
     <row r="887">
       <c r="A887" s="2" t="n">
-        <v>45882</v>
+        <v>45876</v>
       </c>
       <c r="B887" t="n">
-        <v>-3.096493375292383</v>
+        <v>-3.01835103839163</v>
       </c>
     </row>
     <row r="888">
       <c r="A888" s="2" t="n">
-        <v>45883</v>
+        <v>45877</v>
       </c>
       <c r="B888" t="n">
-        <v>-3.073644933324576</v>
+        <v>-3.013942582051172</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" s="2" t="n">
-        <v>45884</v>
+        <v>45880</v>
       </c>
       <c r="B889" t="n">
-        <v>-3.089946730923856</v>
+        <v>-2.980717687824618</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" s="2" t="n">
-        <v>45887</v>
+        <v>45881</v>
       </c>
       <c r="B890" t="n">
-        <v>-3.095218552976116</v>
+        <v>-2.964458466207342</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" s="2" t="n">
-        <v>45888</v>
+        <v>45882</v>
       </c>
       <c r="B891" t="n">
-        <v>-3.028495358707897</v>
+        <v>-3.076150342888749</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" s="2" t="n">
-        <v>45889</v>
+        <v>45883</v>
       </c>
       <c r="B892" t="n">
-        <v>-2.994758344770926</v>
+        <v>-3.052441055172573</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" s="2" t="n">
-        <v>45890</v>
+        <v>45884</v>
       </c>
       <c r="B893" t="n">
-        <v>-2.995244772399206</v>
+        <v>-3.066836527329603</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" s="2" t="n">
-        <v>45891</v>
+        <v>45887</v>
       </c>
       <c r="B894" t="n">
-        <v>-2.999459321323656</v>
+        <v>-3.073582011779704</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" s="2" t="n">
-        <v>45894</v>
+        <v>45888</v>
       </c>
       <c r="B895" t="n">
-        <v>-3.068994840458632</v>
+        <v>-3.011736712252203</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" s="2" t="n">
-        <v>45895</v>
+        <v>45889</v>
       </c>
       <c r="B896" t="n">
-        <v>-3.057755538199712</v>
+        <v>-2.981272207088278</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" s="2" t="n">
-        <v>45896</v>
+        <v>45890</v>
       </c>
       <c r="B897" t="n">
-        <v>-3.092832936536439</v>
+        <v>-2.981640099615229</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" s="2" t="n">
-        <v>45897</v>
+        <v>45891</v>
       </c>
       <c r="B898" t="n">
-        <v>-3.067327626285916</v>
+        <v>-2.980583805452403</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" s="2" t="n">
-        <v>45898</v>
+        <v>45894</v>
       </c>
       <c r="B899" t="n">
-        <v>-3.00106959457304</v>
+        <v>-3.056168951384908</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" s="2" t="n">
-        <v>45901</v>
+        <v>45895</v>
       </c>
       <c r="B900" t="n">
-        <v>-3.067168721982703</v>
+        <v>-3.049511539146685</v>
       </c>
     </row>
     <row r="901">
       <c r="A901" s="2" t="n">
-        <v>45902</v>
+        <v>45896</v>
       </c>
       <c r="B901" t="n">
-        <v>-3.0213259277171</v>
+        <v>-3.084315439392487</v>
       </c>
     </row>
     <row r="902">
       <c r="A902" s="2" t="n">
-        <v>45903</v>
+        <v>45897</v>
       </c>
       <c r="B902" t="n">
-        <v>-3.018888457677783</v>
+        <v>-3.057070089855172</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" s="2" t="n">
-        <v>45904</v>
+        <v>45898</v>
       </c>
       <c r="B903" t="n">
-        <v>-3.032884875540597</v>
+        <v>-2.999870442891959</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" s="2" t="n">
-        <v>45905</v>
+        <v>45901</v>
       </c>
       <c r="B904" t="n">
-        <v>-3.072211052428064</v>
+        <v>-3.071397101594323</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" s="2" t="n">
-        <v>45908</v>
+        <v>45902</v>
       </c>
       <c r="B905" t="n">
-        <v>-3.08406344454246</v>
+        <v>-3.020459386581095</v>
       </c>
     </row>
     <row r="906">
       <c r="A906" s="2" t="n">
-        <v>45909</v>
+        <v>45903</v>
       </c>
       <c r="B906" t="n">
-        <v>-3.061686493915049</v>
+        <v>-3.017807743794833</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" s="2" t="n">
-        <v>45910</v>
+        <v>45904</v>
       </c>
       <c r="B907" t="n">
-        <v>-3.031471138059004</v>
+        <v>-3.031785118644948</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" s="2" t="n">
-        <v>45911</v>
+        <v>45905</v>
       </c>
       <c r="B908" t="n">
-        <v>-2.980530972722766</v>
+        <v>-3.07105327477282</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" s="2" t="n">
-        <v>45912</v>
+        <v>45908</v>
       </c>
       <c r="B909" t="n">
-        <v>-2.947062867885447</v>
+        <v>-3.086716704787435</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" s="2" t="n">
-        <v>45915</v>
+        <v>45909</v>
       </c>
       <c r="B910" t="n">
-        <v>-2.947580280336366</v>
+        <v>-3.064238654090164</v>
       </c>
     </row>
     <row r="911">
       <c r="A911" s="2" t="n">
-        <v>45916</v>
+        <v>45910</v>
       </c>
       <c r="B911" t="n">
-        <v>-2.838043041675745</v>
+        <v>-3.030645959308118</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" s="2" t="n">
-        <v>45917</v>
+        <v>45911</v>
       </c>
       <c r="B912" t="n">
-        <v>-2.790836421068529</v>
+        <v>-2.98058268897636</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" s="2" t="n">
-        <v>45918</v>
+        <v>45912</v>
       </c>
       <c r="B913" t="n">
-        <v>-2.806724880349707</v>
+        <v>-2.948569373294331</v>
       </c>
     </row>
     <row r="914">
       <c r="A914" s="2" t="n">
-        <v>45919</v>
+        <v>45915</v>
       </c>
       <c r="B914" t="n">
-        <v>-2.794732417632713</v>
+        <v>-2.950061381738447</v>
       </c>
     </row>
     <row r="915">
       <c r="A915" s="2" t="n">
-        <v>45922</v>
+        <v>45916</v>
       </c>
       <c r="B915" t="n">
-        <v>-2.798078481793572</v>
+        <v>-2.840190411638228</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" s="2" t="n">
-        <v>45923</v>
+        <v>45917</v>
       </c>
       <c r="B916" t="n">
-        <v>-2.796568727265701</v>
+        <v>-2.791236013502842</v>
       </c>
     </row>
     <row r="917">
       <c r="A917" s="2" t="n">
-        <v>45924</v>
+        <v>45918</v>
       </c>
       <c r="B917" t="n">
-        <v>-2.812803787992221</v>
+        <v>-2.80590299439082</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" s="2" t="n">
-        <v>45925</v>
+        <v>45919</v>
       </c>
       <c r="B918" t="n">
-        <v>-2.812590460747754</v>
+        <v>-2.790995502005928</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" s="2" t="n">
-        <v>45926</v>
+        <v>45922</v>
       </c>
       <c r="B919" t="n">
-        <v>-2.767958879120647</v>
+        <v>-2.795322768852792</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" s="2" t="n">
-        <v>45929</v>
+        <v>45923</v>
       </c>
       <c r="B920" t="n">
-        <v>-2.788786327447847</v>
+        <v>-2.792560358440306</v>
       </c>
     </row>
     <row r="921">
       <c r="A921" s="2" t="n">
-        <v>45930</v>
+        <v>45924</v>
       </c>
       <c r="B921" t="n">
-        <v>-2.793921820230309</v>
+        <v>-2.808635337128734</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" s="2" t="n">
-        <v>45932</v>
+        <v>45925</v>
       </c>
       <c r="B922" t="n">
-        <v>-2.818068999650934</v>
+        <v>-2.808255019798812</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" s="2" t="n">
-        <v>45933</v>
+        <v>45926</v>
       </c>
       <c r="B923" t="n">
-        <v>-2.822690064039994</v>
+        <v>-2.769395744104994</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" s="2" t="n">
-        <v>45936</v>
+        <v>45929</v>
       </c>
       <c r="B924" t="n">
-        <v>-2.769046859316801</v>
+        <v>-2.785162791469375</v>
       </c>
     </row>
     <row r="925">
       <c r="A925" s="2" t="n">
-        <v>45938</v>
+        <v>45930</v>
       </c>
       <c r="B925" t="n">
-        <v>-2.759303974935824</v>
+        <v>-2.791254950764595</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" s="2" t="n">
-        <v>45939</v>
+        <v>45932</v>
       </c>
       <c r="B926" t="n">
-        <v>-2.727231941784289</v>
+        <v>-2.815876781051241</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" s="2" t="n">
-        <v>45940</v>
+        <v>45933</v>
       </c>
       <c r="B927" t="n">
-        <v>-2.758248360010338</v>
+        <v>-2.821733096677341</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" s="2" t="n">
-        <v>45943</v>
+        <v>45936</v>
       </c>
       <c r="B928" t="n">
-        <v>-2.782671630048673</v>
+        <v>-2.768148320438089</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" s="2" t="n">
-        <v>45944</v>
+        <v>45938</v>
       </c>
       <c r="B929" t="n">
-        <v>-2.8133740275218</v>
+        <v>-2.758415413028391</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" s="2" t="n">
-        <v>45945</v>
+        <v>45939</v>
       </c>
       <c r="B930" t="n">
-        <v>-2.813479231784959</v>
+        <v>-2.722999894392583</v>
       </c>
     </row>
     <row r="931">
       <c r="A931" s="2" t="n">
-        <v>45946</v>
+        <v>45940</v>
       </c>
       <c r="B931" t="n">
-        <v>-2.804995451527497</v>
+        <v>-2.754065739065039</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" s="2" t="n">
-        <v>45947</v>
+        <v>45943</v>
       </c>
       <c r="B932" t="n">
-        <v>-2.858004714283982</v>
+        <v>-2.778251376100922</v>
       </c>
     </row>
     <row r="933">
       <c r="A933" s="2" t="n">
-        <v>45950</v>
+        <v>45944</v>
       </c>
       <c r="B933" t="n">
-        <v>-2.962467845853187</v>
+        <v>-2.808645840963925</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" s="2" t="n">
-        <v>45951</v>
+        <v>45945</v>
       </c>
       <c r="B934" t="n">
-        <v>-2.970998141039484</v>
+        <v>-2.806957237442357</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" s="2" t="n">
-        <v>45952</v>
+        <v>45946</v>
       </c>
       <c r="B935" t="n">
-        <v>-2.878611393182115</v>
+        <v>-2.799353698572163</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" s="2" t="n">
-        <v>45953</v>
+        <v>45947</v>
       </c>
       <c r="B936" t="n">
-        <v>-2.835822618266073</v>
+        <v>-2.851623848356606</v>
       </c>
     </row>
     <row r="937">
       <c r="A937" s="2" t="n">
-        <v>45954</v>
+        <v>45950</v>
       </c>
       <c r="B937" t="n">
-        <v>-2.833507812176524</v>
+        <v>-2.955506837096441</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" s="2" t="n">
-        <v>45957</v>
+        <v>45951</v>
       </c>
       <c r="B938" t="n">
-        <v>-2.84492906800858</v>
+        <v>-2.963911826345568</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" s="2" t="n">
-        <v>45958</v>
+        <v>45952</v>
       </c>
       <c r="B939" t="n">
-        <v>-2.845637213201779</v>
+        <v>-2.876332342291734</v>
       </c>
     </row>
     <row r="940">
       <c r="A940" s="2" t="n">
-        <v>45960</v>
+        <v>45953</v>
       </c>
       <c r="B940" t="n">
-        <v>-2.926331765454811</v>
+        <v>-2.834494361735632</v>
       </c>
     </row>
     <row r="941">
       <c r="A941" s="2" t="n">
-        <v>45961</v>
+        <v>45954</v>
       </c>
       <c r="B941" t="n">
-        <v>-2.950427672039586</v>
+        <v>-2.832199751702936</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" s="2" t="n">
-        <v>45964</v>
+        <v>45957</v>
       </c>
       <c r="B942" t="n">
-        <v>-2.960550022103135</v>
+        <v>-2.843447711994168</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" s="2" t="n">
-        <v>45965</v>
+        <v>45958</v>
       </c>
       <c r="B943" t="n">
-        <v>-2.945936376421415</v>
+        <v>-2.844089118343055</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" s="2" t="n">
-        <v>45966</v>
+        <v>45960</v>
       </c>
       <c r="B944" t="n">
-        <v>-2.93320404609698</v>
+        <v>-2.919101940337626</v>
       </c>
     </row>
     <row r="945">
       <c r="A945" s="2" t="n">
-        <v>45967</v>
+        <v>45961</v>
       </c>
       <c r="B945" t="n">
-        <v>-3.014239205600549</v>
+        <v>-2.942010495264219</v>
       </c>
     </row>
     <row r="946">
       <c r="A946" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B946" t="n">
+        <v>-2.952194676928139</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B947" t="n">
+        <v>-2.941055913125312</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B948" t="n">
+        <v>-2.930590222462363</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B949" t="n">
+        <v>-3.011233350133498</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="2" t="n">
         <v>45968</v>
       </c>
-      <c r="B946" t="n">
-        <v>-3.010467331588292</v>
+      <c r="B950" t="n">
+        <v>-3.003996318478407</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="2" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B951" t="n">
+        <v>-3.021087851255984</v>
       </c>
     </row>
   </sheetData>
